--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU17"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-12 12:00:00</t>
+          <t>2026-10-12 09:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-12 12:00:00</t>
+          <t>2026-10-12 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-10-12 13:00:00</t>
+          <t>2026-10-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-12 13:30:00</t>
+          <t>2026-10-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-12 14:00:00</t>
+          <t>2026-10-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-12 14:00:00</t>
+          <t>2026-10-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-12 14:45:00</t>
+          <t>2026-10-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-12 15:00:00</t>
+          <t>2026-10-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-12 15:45:00</t>
+          <t>2026-10-12 11:15:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00:00</t>
+          <t>2026-10-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-12 17:30:00</t>
+          <t>2026-10-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-12 19:30:00</t>
+          <t>2026-10-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-12 21:00:00</t>
+          <t>2026-10-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,156 +3033,8306 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Poland 1. Liga</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Stal Rzeszów</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lechia Gdańsk</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>2.91</v>
+      </c>
+      <c r="O17">
+        <v>4.12</v>
+      </c>
+      <c r="P17">
+        <v>2.16</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Saba</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ashdod</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Shalem</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hapoel Ra'anana</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Hapoel Rishon LeZion</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Maccabi Kabilio Jaffa</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motor Lublin</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cyprus First Division</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AEK Larnaca</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Omonia Aradippou</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>1.29</v>
+      </c>
+      <c r="O22">
+        <v>5</v>
+      </c>
+      <c r="P22">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SD Eibar</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>1.63</v>
+      </c>
+      <c r="O24">
+        <v>4.53</v>
+      </c>
+      <c r="P24">
+        <v>5.56</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>1.58</v>
+      </c>
+      <c r="AB24">
+        <v>2.25</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Eyüpspor</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Göztepe</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pyramids FC</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Smouha SC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ghazl El Mehalla</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Benfica II</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Forge FC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>York9 FC</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>1.76</v>
+      </c>
+      <c r="O31">
+        <v>3.78</v>
+      </c>
+      <c r="P31">
+        <v>4.23</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>1.34</v>
+      </c>
+      <c r="O32">
+        <v>4.95</v>
+      </c>
+      <c r="P32">
+        <v>8.25</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Hapoel Katamon</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hungary NB II</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BVSC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Soroksár SC</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Unión San Felipe</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LFK Mladost Lučani</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>OFK Beograd</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>2.58</v>
+      </c>
+      <c r="O38">
+        <v>3.58</v>
+      </c>
+      <c r="P38">
+        <v>2.58</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>2.07</v>
+      </c>
+      <c r="AB38">
+        <v>1.72</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Universitatea Cluj</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rapid Bucureşti</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>2.5</v>
+      </c>
+      <c r="O39">
+        <v>3.1</v>
+      </c>
+      <c r="P39">
+        <v>2.75</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pescara</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nuova Monterosi</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Spain Primera Division RFEF Group 1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CD Lugo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>UD Logroñés</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GKS Katowice</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Wieczysta Kraków</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Barletta</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Cavese</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Picerno</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>France Ligue 2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Gualberto Villarroel SJ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>2.29</v>
+      </c>
+      <c r="O50">
+        <v>3.45</v>
+      </c>
+      <c r="P50">
+        <v>2.92</v>
+      </c>
+      <c r="Q50">
+        <v>2.85</v>
+      </c>
+      <c r="R50">
+        <v>2.15</v>
+      </c>
+      <c r="S50">
+        <v>1.35</v>
+      </c>
+      <c r="T50">
+        <v>2.94</v>
+      </c>
+      <c r="U50">
+        <v>2.65</v>
+      </c>
+      <c r="V50">
+        <v>1.42</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
+        <v>1.23</v>
+      </c>
+      <c r="Z50">
+        <v>3.44</v>
+      </c>
+      <c r="AA50">
+        <v>1.84</v>
+      </c>
+      <c r="AB50">
+        <v>1.93</v>
+      </c>
+      <c r="AC50">
+        <v>2.94</v>
+      </c>
+      <c r="AD50">
+        <v>1.31</v>
+      </c>
+      <c r="AE50">
+        <v>1.09</v>
+      </c>
+      <c r="AF50">
+        <v>1.65</v>
+      </c>
+      <c r="AG50">
+        <v>2.08</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.28</v>
+      </c>
+      <c r="AK50">
+        <v>1.59</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CD Tenerife</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1</v>
+      </c>
+      <c r="AN53">
+        <v>-1</v>
+      </c>
+      <c r="AO53">
+        <v>-1</v>
+      </c>
+      <c r="AP53">
+        <v>-1</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>1.92</v>
+      </c>
+      <c r="O54">
+        <v>3.67</v>
+      </c>
+      <c r="P54">
+        <v>4.22</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>1.98</v>
+      </c>
+      <c r="AB54">
+        <v>1.72</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>-1</v>
+      </c>
+      <c r="AN54">
+        <v>-1</v>
+      </c>
+      <c r="AO54">
+        <v>-1</v>
+      </c>
+      <c r="AP54">
+        <v>-1</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-1</v>
+      </c>
+      <c r="AN55">
+        <v>-1</v>
+      </c>
+      <c r="AO55">
+        <v>-1</v>
+      </c>
+      <c r="AP55">
+        <v>-1</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>HFX Wanderers FC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>-1</v>
+      </c>
+      <c r="AN57">
+        <v>-1</v>
+      </c>
+      <c r="AO57">
+        <v>-1</v>
+      </c>
+      <c r="AP57">
+        <v>-1</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Racing United</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>1.8</v>
+      </c>
+      <c r="AB59">
+        <v>2</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Club Always Ready</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-1</v>
+      </c>
+      <c r="AN60">
+        <v>-1</v>
+      </c>
+      <c r="AO60">
+        <v>-1</v>
+      </c>
+      <c r="AP60">
+        <v>-1</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>-1</v>
+      </c>
+      <c r="AN61">
+        <v>-1</v>
+      </c>
+      <c r="AO61">
+        <v>-1</v>
+      </c>
+      <c r="AP61">
+        <v>-1</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>0</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-1</v>
+      </c>
+      <c r="AN62">
+        <v>-1</v>
+      </c>
+      <c r="AO62">
+        <v>-1</v>
+      </c>
+      <c r="AP62">
+        <v>-1</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>3.55</v>
+      </c>
+      <c r="O63">
+        <v>3.49</v>
+      </c>
+      <c r="P63">
+        <v>2.11</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>1.98</v>
+      </c>
+      <c r="AB63">
+        <v>1.88</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>2.19</v>
+      </c>
+      <c r="O65">
+        <v>3.57</v>
+      </c>
+      <c r="P65">
+        <v>3.28</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-1</v>
-      </c>
-      <c r="AN17">
-        <v>-1</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>-1</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>2026-10-12 22:00:00</t>
         </is>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC45">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q51">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2310,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q56">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q28">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G20">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.45</v>
+        <v>1.29</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>2.88</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-12 13:30:00</t>
+          <t>2026-10-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.63</v>
+        <v>2.45</v>
       </c>
       <c r="O24">
-        <v>4.53</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>5.56</v>
+        <v>2.88</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-12 14:00:00</t>
+          <t>2026-10-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="P29">
-        <v>2.61</v>
+        <v>3.33</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="O32">
-        <v>4.95</v>
+        <v>3.78</v>
       </c>
       <c r="P32">
-        <v>8.25</v>
+        <v>4.23</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-12 14:30:00</t>
+          <t>2026-10-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-12 14:45:00</t>
+          <t>2026-10-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-12 15:00:00</t>
+          <t>2026-10-12 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="P39">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-12 15:30:00</t>
+          <t>2026-10-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,17 +7151,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,17 +7314,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-12 15:45:00</t>
+          <t>2026-10-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="O46">
         <v>3.48</v>
       </c>
       <c r="P46">
-        <v>3.27</v>
+        <v>2.45</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB46">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.58</v>
+        <v>2.37</v>
       </c>
       <c r="O47">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P47">
-        <v>2.09</v>
+        <v>3.27</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00:00</t>
+          <t>2026-10-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,68 +8455,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G51">
@@ -8618,68 +8618,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P51">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-12 16:15:00</t>
+          <t>2026-10-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:00</t>
+          <t>2026-10-12 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-12 17:30:00</t>
+          <t>2026-10-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-12 17:30:00</t>
+          <t>2026-10-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G59">
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-12 18:00:00</t>
+          <t>2026-10-12 17:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G60">
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-12 18:15:00</t>
+          <t>2026-10-12 18:00:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-12 18:15:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-12 19:30:00</t>
+          <t>2026-10-12 19:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-12 19:30:00</t>
+          <t>2026-10-12 19:05:00</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.19</v>
+        <v>3.55</v>
       </c>
       <c r="O65">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="P65">
-        <v>3.28</v>
+        <v>2.11</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-10-12 21:00:00</t>
+          <t>2026-10-12 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-12 21:00:00</t>
+          <t>2026-10-12 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11183,156 +11183,645 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>2.19</v>
+      </c>
+      <c r="O67">
+        <v>3.57</v>
+      </c>
+      <c r="P67">
+        <v>3.28</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tru-Juice</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-10-12 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>2026-10-12 22:00:00</t>
         </is>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC28">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10448,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA62">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q45">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -807,55 +807,55 @@
         <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>7.37</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,40 +2274,40 @@
         <v>13</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC12">
         <v>2.25</v>
@@ -2316,13 +2316,13 @@
         <v>1.57</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>2.35</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.96</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>2.16</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>2.78</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>2.88</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,34 +4393,34 @@
         <v>5.56</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA25">
         <v>1.58</v>
@@ -4429,19 +4429,19 @@
         <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>3.33</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>4.23</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>8.25</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>5.7</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
         <v>1.92</v>
@@ -6059,19 +6059,19 @@
         <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>1.49</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -5208,55 +5208,55 @@
         <v>2.61</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="P56">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.96</v>
+        <v>2.78</v>
       </c>
       <c r="O57">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>1.69</v>
+        <v>2.78</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-12 17:30:00</t>
+          <t>2026-10-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G60">
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-12 18:00:00</t>
+          <t>2026-10-12 17:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -11715,7 +11715,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70">

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -4719,55 +4719,55 @@
         <v>3.99</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,34 +4882,34 @@
         <v>5.81</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
         <v>1.95</v>
@@ -4918,19 +4918,19 @@
         <v>1.81</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.53</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P18">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="O27">
-        <v>2.56</v>
+        <v>3.74</v>
       </c>
       <c r="P27">
-        <v>3.99</v>
+        <v>5.81</v>
       </c>
       <c r="Q27">
-        <v>3.21</v>
+        <v>2.11</v>
       </c>
       <c r="R27">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="S27">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="U27">
-        <v>4.7</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.24</v>
+      </c>
+      <c r="Z27">
+        <v>3.34</v>
+      </c>
+      <c r="AA27">
+        <v>1.95</v>
+      </c>
+      <c r="AB27">
+        <v>1.81</v>
+      </c>
+      <c r="AC27">
+        <v>3.04</v>
+      </c>
+      <c r="AD27">
+        <v>1.29</v>
+      </c>
+      <c r="AE27">
+        <v>1.11</v>
+      </c>
+      <c r="AF27">
+        <v>1.85</v>
+      </c>
+      <c r="AG27">
+        <v>1.82</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.13</v>
       </c>
-      <c r="Y27">
-        <v>1.76</v>
-      </c>
-      <c r="Z27">
-        <v>1.92</v>
-      </c>
-      <c r="AA27">
-        <v>3.34</v>
-      </c>
-      <c r="AB27">
-        <v>1.24</v>
-      </c>
-      <c r="AC27">
-        <v>7.6</v>
-      </c>
-      <c r="AD27">
-        <v>1.03</v>
-      </c>
-      <c r="AE27">
-        <v>1.01</v>
-      </c>
-      <c r="AF27">
-        <v>2.7</v>
-      </c>
-      <c r="AG27">
-        <v>1.42</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.44</v>
-      </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="O28">
-        <v>3.74</v>
+        <v>2.56</v>
       </c>
       <c r="P28">
-        <v>5.81</v>
+        <v>3.99</v>
       </c>
       <c r="Q28">
-        <v>2.11</v>
+        <v>3.21</v>
       </c>
       <c r="R28">
-        <v>2.36</v>
+        <v>1.76</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="T28">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>4.7</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
+        <v>1.13</v>
+      </c>
+      <c r="Y28">
+        <v>1.76</v>
+      </c>
+      <c r="Z28">
+        <v>1.92</v>
+      </c>
+      <c r="AA28">
+        <v>3.34</v>
+      </c>
+      <c r="AB28">
+        <v>1.24</v>
+      </c>
+      <c r="AC28">
+        <v>7.6</v>
+      </c>
+      <c r="AD28">
+        <v>1.03</v>
+      </c>
+      <c r="AE28">
         <v>1.01</v>
       </c>
-      <c r="Y28">
-        <v>1.24</v>
-      </c>
-      <c r="Z28">
-        <v>3.34</v>
-      </c>
-      <c r="AA28">
-        <v>1.95</v>
-      </c>
-      <c r="AB28">
-        <v>1.81</v>
-      </c>
-      <c r="AC28">
-        <v>3.04</v>
-      </c>
-      <c r="AD28">
-        <v>1.29</v>
-      </c>
-      <c r="AE28">
-        <v>1.11</v>
-      </c>
       <c r="AF28">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG28">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AK28">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6675,34 +6675,34 @@
         <v>2.58</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AA39">
         <v>2.07</v>
@@ -6711,19 +6711,19 @@
         <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>4.31</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>2.65</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>2.97</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>3.05</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>4.66</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,34 +7816,34 @@
         <v>2.45</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA46">
         <v>1.7</v>
@@ -7852,19 +7852,19 @@
         <v>2</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,34 +7979,34 @@
         <v>3.27</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA47">
         <v>1.98</v>
@@ -8015,19 +8015,19 @@
         <v>1.73</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,34 +8142,34 @@
         <v>2.09</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA48">
         <v>1.65</v>
@@ -8178,19 +8178,19 @@
         <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>2.3</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>4.22</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA55">
         <v>1.98</v>
@@ -9319,19 +9319,19 @@
         <v>1.72</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>19</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10913,34 +10913,34 @@
         <v>2.11</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA65">
         <v>1.98</v>
@@ -10949,19 +10949,19 @@
         <v>1.88</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>3.28</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q68">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="O5">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>7.37</v>
+        <v>5.6</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
         <v>2.6</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.07</v>
@@ -1157,47 +1157,47 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
+        <v>2.97</v>
+      </c>
+      <c r="AD5">
+        <v>1.3</v>
+      </c>
+      <c r="AE5">
+        <v>1.08</v>
+      </c>
+      <c r="AF5">
+        <v>1.97</v>
+      </c>
+      <c r="AG5">
+        <v>1.73</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.08</v>
+      </c>
+      <c r="AK5">
         <v>2.88</v>
-      </c>
-      <c r="AD5">
-        <v>1.32</v>
-      </c>
-      <c r="AE5">
-        <v>1.09</v>
-      </c>
-      <c r="AF5">
-        <v>1.98</v>
-      </c>
-      <c r="AG5">
-        <v>1.72</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.17</v>
-      </c>
-      <c r="AK5">
-        <v>2.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1948,34 +1948,34 @@
         <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
         <v>1.79</v>
@@ -1984,19 +1984,19 @@
         <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O12">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="P12">
         <v>13</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
         <v>3</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T12">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="U12">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W12">
         <v>1.18</v>
@@ -2298,7 +2298,7 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
         <v>5.25</v>
@@ -2310,10 +2310,10 @@
         <v>2.7</v>
       </c>
       <c r="AC12">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AD12">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE12">
         <v>1.25</v>
@@ -2322,7 +2322,7 @@
         <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
         <v>2.4</v>
@@ -2781,37 +2781,37 @@
         <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE15">
         <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.85</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q3">
         <v>2.55</v>
@@ -813,49 +813,49 @@
         <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
         <v>2.63</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
         <v>1.7</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
         <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V11">
         <v>1.35</v>
@@ -2132,22 +2132,22 @@
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="Z11">
         <v>3</v>
       </c>
       <c r="AA11">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD11">
         <v>1.22</v>
@@ -2156,10 +2156,10 @@
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         <v>2.6</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q13">
         <v>3.16</v>
@@ -2458,7 +2458,7 @@
         <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.17</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AK13">
         <v>1.37</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="O14">
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="Q14">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R14">
         <v>1.95</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.53</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P20">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>4.68</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>7.5</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>3.1</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -8305,22 +8305,22 @@
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R49">
         <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U49">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V49">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
         <v>1.07</v>
@@ -8329,10 +8329,10 @@
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
         <v>1.8</v>
@@ -8341,7 +8341,7 @@
         <v>1.87</v>
       </c>
       <c r="AC49">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD49">
         <v>1.33</v>
@@ -8369,7 +8369,7 @@
         <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="O51">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="P51">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="Q51">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.44</v>
+        <v>3.72</v>
       </c>
       <c r="AA51">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC51">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AD51">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="O54">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>4.68</v>
+        <v>4</v>
       </c>
       <c r="Q54">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S54">
         <v>1.4</v>
       </c>
       <c r="T54">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="U54">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V54">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
         <v>1.29</v>
       </c>
       <c r="Z54">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="AA54">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB54">
         <v>1.75</v>
       </c>
       <c r="AC54">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="AD54">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE54">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF54">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG54">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL54">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O54">
         <v>3.4</v>
       </c>
       <c r="P54">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="Q54">
         <v>2.4</v>
@@ -9126,16 +9126,16 @@
         <v>2.21</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="U54">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W54">
         <v>1.07</v>
@@ -9150,13 +9150,13 @@
         <v>3.19</v>
       </c>
       <c r="AA54">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC54">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD54">
         <v>1.25</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="R63">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="S63">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U63">
+        <v>1.81</v>
+      </c>
+      <c r="V63">
         <v>1.93</v>
       </c>
-      <c r="V63">
-        <v>1.79</v>
-      </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z63">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA63">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AB63">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="AC63">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AD63">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="AE63">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AF63">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AG63">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK63">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q65">
         <v>3.7</v>
@@ -10919,7 +10919,7 @@
         <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
         <v>3</v>
@@ -10931,34 +10931,34 @@
         <v>1.41</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z65">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB65">
         <v>1.88</v>
       </c>
       <c r="AC65">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD65">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG65">
         <v>2</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
         <v>1.29</v>
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="O66">
         <v>4.33</v>
       </c>
       <c r="P66">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q66">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S66">
         <v>1.35</v>
       </c>
       <c r="T66">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U66">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="V66">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
         <v>1.08</v>
@@ -11100,31 +11100,31 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="AA66">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC66">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="AD66">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE66">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF66">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AG66">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK66">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AL66">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q5">
         <v>1.99</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="O8">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="P8">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="Q8">
         <v>3.75</v>
@@ -1628,10 +1628,10 @@
         <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U8">
         <v>4</v>
@@ -1640,28 +1640,28 @@
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z8">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AA8">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AB8">
         <v>1.39</v>
       </c>
       <c r="AC8">
-        <v>4.9</v>
+        <v>5.57</v>
       </c>
       <c r="AD8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1686,7 +1686,7 @@
         <v>1.4</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,55 +1776,55 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O9">
+        <v>2.92</v>
+      </c>
+      <c r="P9">
+        <v>3.6</v>
+      </c>
+      <c r="Q9">
         <v>2.83</v>
       </c>
-      <c r="P9">
-        <v>3.8</v>
-      </c>
-      <c r="Q9">
-        <v>2.88</v>
-      </c>
       <c r="R9">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V9">
         <v>1.24</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z9">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AA9">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB9">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC9">
-        <v>4.95</v>
+        <v>5.53</v>
       </c>
       <c r="AD9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
@@ -1978,10 +1978,10 @@
         <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AC10">
         <v>2.98</v>
@@ -2292,7 +2292,7 @@
         <v>1.71</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,7 +2301,7 @@
         <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="AA12">
         <v>1.4</v>
@@ -2310,7 +2310,7 @@
         <v>2.7</v>
       </c>
       <c r="AC12">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AD12">
         <v>1.68</v>
@@ -2322,7 +2322,7 @@
         <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2600,10 +2600,10 @@
         <v>2.9</v>
       </c>
       <c r="Q14">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S14">
         <v>1.45</v>
@@ -2612,31 +2612,31 @@
         <v>2.5</v>
       </c>
       <c r="U14">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="Z14">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AA14">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="AB14">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC14">
-        <v>3.82</v>
+        <v>4.75</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
@@ -2645,10 +2645,10 @@
         <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q23">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="AA23">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB23">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AC23">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AG23">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK23">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="O25">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="P25">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="Q25">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="R25">
         <v>2.4</v>
@@ -4402,10 +4402,10 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.8</v>
+        <v>3.26</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
         <v>1.57</v>
@@ -4414,28 +4414,28 @@
         <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA25">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AB25">
         <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AD25">
         <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK25">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4713,19 +4713,19 @@
         <v>1.5</v>
       </c>
       <c r="O27">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>5.81</v>
+        <v>4.65</v>
       </c>
       <c r="Q27">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
         <v>2.86</v>
@@ -4737,34 +4737,34 @@
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB27">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG27">
         <v>1.82</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
         <v>2.24</v>
@@ -4879,10 +4879,10 @@
         <v>2.56</v>
       </c>
       <c r="P28">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
         <v>1.76</v>
@@ -4897,7 +4897,7 @@
         <v>4.7</v>
       </c>
       <c r="V28">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="W28">
         <v>1.02</v>
@@ -4906,10 +4906,10 @@
         <v>1.13</v>
       </c>
       <c r="Y28">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Z28">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AA28">
         <v>3.34</v>
@@ -4927,7 +4927,7 @@
         <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AG28">
         <v>1.42</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5857,28 +5857,28 @@
         <v>4.25</v>
       </c>
       <c r="P34">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q34">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
         <v>3.55</v>
       </c>
       <c r="U34">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="V34">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5896,19 +5896,19 @@
         <v>2.4</v>
       </c>
       <c r="AC34">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD34">
         <v>1.62</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
         <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O35">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>5.7</v>
+        <v>5.56</v>
       </c>
       <c r="Q35">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
         <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6047,22 +6047,22 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA35">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE35">
         <v>1.06</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6835,25 +6835,25 @@
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="Q40">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R40">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="U40">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.06</v>
@@ -6865,28 +6865,28 @@
         <v>1.31</v>
       </c>
       <c r="Z40">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA40">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD40">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG40">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O41">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.31</v>
+        <v>4.1</v>
       </c>
       <c r="Q41">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R41">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z41">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA41">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB41">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC41">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AG41">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="O42">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="Q42">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R42">
         <v>2</v>
@@ -7173,46 +7173,46 @@
         <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U42">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="V42">
         <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AA42">
         <v>2.15</v>
       </c>
       <c r="AB42">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC42">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="AD42">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O44">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="O45">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>4.66</v>
+        <v>4.1</v>
       </c>
       <c r="Q45">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U45">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W45">
         <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z45">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA45">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB45">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD45">
+        <v>1.25</v>
+      </c>
+      <c r="AE45">
+        <v>1.06</v>
+      </c>
+      <c r="AF45">
+        <v>1.79</v>
+      </c>
+      <c r="AG45">
+        <v>1.88</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.24</v>
       </c>
-      <c r="AE45">
-        <v>1.05</v>
-      </c>
-      <c r="AF45">
+      <c r="AK45">
         <v>1.85</v>
-      </c>
-      <c r="AG45">
-        <v>1.82</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.22</v>
-      </c>
-      <c r="AK45">
-        <v>1.92</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O47">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P47">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="Q47">
         <v>2.8</v>
@@ -7985,7 +7985,7 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T47">
         <v>2.57</v>
@@ -8000,22 +8000,22 @@
         <v>1.04</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z47">
         <v>2.82</v>
       </c>
       <c r="AA47">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC47">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD47">
         <v>1.23</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -2111,19 +2111,19 @@
         <v>2.88</v>
       </c>
       <c r="Q11">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
         <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
         <v>1.35</v>
@@ -2132,10 +2132,10 @@
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
         <v>3</v>
@@ -2147,7 +2147,7 @@
         <v>1.73</v>
       </c>
       <c r="AC11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
         <v>1.22</v>
@@ -2434,7 +2434,7 @@
         <v>3.3</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
         <v>3.16</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="O17">
-        <v>4.12</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>1.62</v>
@@ -3113,31 +3113,31 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA17">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB17">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD17">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
         <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O19">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>4.6</v>
       </c>
       <c r="P20">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="O21">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="P21">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
       </c>
       <c r="R21">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="S21">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.03</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK21">
         <v>1.5</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="P24">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="Q24">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
         <v>1.41</v>
@@ -4245,7 +4245,7 @@
         <v>2.83</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
         <v>1.05</v>
@@ -4263,10 +4263,10 @@
         <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
         <v>1.62</v>
@@ -4550,7 +4550,7 @@
         <v>3.6</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
         <v>1.95</v>
@@ -4562,16 +4562,16 @@
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U26">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
         <v>1.08</v>
@@ -4580,7 +4580,7 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
         <v>4</v>
@@ -4592,19 +4592,19 @@
         <v>1.99</v>
       </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AK26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5051,19 +5051,19 @@
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V29">
         <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5072,25 +5072,25 @@
         <v>1.31</v>
       </c>
       <c r="Z29">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="AA29">
         <v>2.07</v>
       </c>
       <c r="AB29">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC29">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG29">
         <v>1.91</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,43 +5199,43 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>2.61</v>
+        <v>2.36</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
         <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
         <v>1.58</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z30">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA30">
         <v>1.53</v>
@@ -5250,13 +5250,13 @@
         <v>1.55</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
         <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O31">
         <v>5</v>
       </c>
       <c r="P31">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5528,19 +5528,19 @@
         <v>1.76</v>
       </c>
       <c r="O32">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="Q32">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
         <v>2.87</v>
@@ -5552,37 +5552,37 @@
         <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z32">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="AA32">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AB32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC32">
         <v>2.78</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
         <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="O33">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R33">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
         <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="V33">
         <v>1.57</v>
@@ -5724,28 +5724,28 @@
         <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
         <v>2.35</v>
       </c>
       <c r="AD33">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE33">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG33">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>5.52</v>
+        <v>4.91</v>
       </c>
       <c r="O36">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="Q36">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T36">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U36">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V36">
         <v>1.56</v>
@@ -6210,28 +6210,28 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA36">
         <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD36">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG36">
         <v>2.15</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.18</v>
+        <v>2.25</v>
       </c>
       <c r="AK36">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="O38">
         <v>3.55</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6666,28 +6666,28 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.58</v>
+        <v>3.33</v>
       </c>
       <c r="P39">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R39">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T39">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="U39">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6696,34 +6696,34 @@
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z39">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB39">
         <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK39">
         <v>1.4</v>
@@ -7348,7 +7348,7 @@
         <v>1.1</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
         <v>1.14</v>
@@ -7375,7 +7375,7 @@
         <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7807,34 +7807,34 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="O46">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q46">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="R46">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V46">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7849,7 +7849,7 @@
         <v>1.7</v>
       </c>
       <c r="AB46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
         <v>2.66</v>
@@ -7861,7 +7861,7 @@
         <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG46">
         <v>2.25</v>
@@ -7880,7 +7880,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="O48">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
       </c>
       <c r="R48">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.29</v>
@@ -8160,7 +8160,7 @@
         <v>1.53</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8172,25 +8172,25 @@
         <v>4.3</v>
       </c>
       <c r="AA48">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AC48">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AD48">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
         <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.76</v>
+        <v>1.31</v>
       </c>
       <c r="AK48">
         <v>1.36</v>
@@ -8468,10 +8468,10 @@
         <v>2.83</v>
       </c>
       <c r="Q50">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8498,7 +8498,7 @@
         <v>5.25</v>
       </c>
       <c r="AA50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
         <v>2.56</v>
@@ -8532,7 +8532,7 @@
         <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8634,22 +8634,22 @@
         <v>2.54</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
         <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -8676,7 +8676,7 @@
         <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
         <v>2.14</v>
@@ -8695,7 +8695,7 @@
         <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
+        <v>2.62</v>
+      </c>
+      <c r="O52">
         <v>3</v>
       </c>
-      <c r="O52">
-        <v>3.1</v>
-      </c>
       <c r="P52">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
         <v>3.44</v>
@@ -8806,16 +8806,16 @@
         <v>2.6</v>
       </c>
       <c r="U52">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V52">
         <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
         <v>1.29</v>
@@ -8833,7 +8833,7 @@
         <v>3.9</v>
       </c>
       <c r="AD52">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
         <v>1.05</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK52">
         <v>1.4</v>
@@ -8954,10 +8954,10 @@
         <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q53">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8966,7 +8966,7 @@
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="U53">
         <v>2.88</v>
@@ -8975,16 +8975,16 @@
         <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z53">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AA53">
         <v>2.07</v>
@@ -8996,13 +8996,13 @@
         <v>3.65</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG53">
         <v>2</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="O55">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="Q55">
         <v>2.36</v>
@@ -9295,10 +9295,10 @@
         <v>2.62</v>
       </c>
       <c r="U55">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W55">
         <v>1.07</v>
@@ -9310,13 +9310,13 @@
         <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA55">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB55">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC55">
         <v>3.28</v>
@@ -9328,10 +9328,10 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG55">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9443,10 +9443,10 @@
         <v>3.9</v>
       </c>
       <c r="P56">
-        <v>5.1</v>
+        <v>6.54</v>
       </c>
       <c r="Q56">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R56">
         <v>2.2</v>
@@ -9467,34 +9467,34 @@
         <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z56">
         <v>3.96</v>
       </c>
       <c r="AA56">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB56">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC56">
         <v>2.88</v>
       </c>
       <c r="AD56">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF56">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG56">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
         <v>3.45</v>
       </c>
       <c r="P60">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,19 +10258,19 @@
         <v>10</v>
       </c>
       <c r="P61">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="Q61">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="R61">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="S61">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T61">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="U61">
         <v>1.73</v>
@@ -10279,7 +10279,7 @@
         <v>2.3</v>
       </c>
       <c r="W61">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         <v>1.01</v>
       </c>
       <c r="Z61">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA61">
         <v>1.19</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK61">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O3">
         <v>3.34</v>
@@ -807,19 +807,19 @@
         <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
         <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
         <v>1.41</v>
@@ -828,25 +828,25 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC3">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="AD3">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
         <v>1.12</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="T8">
         <v>2.3</v>
@@ -1640,13 +1640,13 @@
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z8">
         <v>2.29</v>
@@ -1785,7 +1785,7 @@
         <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>1.95</v>
@@ -1806,13 +1806,13 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
         <v>1.56</v>
       </c>
       <c r="Z9">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AA9">
         <v>2.81</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>5.05</v>
+        <v>4.3</v>
       </c>
       <c r="O10">
         <v>3.8</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q10">
         <v>5.41</v>
       </c>
       <c r="R10">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
         <v>1.07</v>
@@ -1972,22 +1972,22 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AB10">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC10">
         <v>2.98</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
         <v>1.1</v>
@@ -2132,7 +2132,7 @@
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.29</v>
@@ -2141,10 +2141,10 @@
         <v>3</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
         <v>3.9</v>
@@ -2268,43 +2268,43 @@
         <v>1.18</v>
       </c>
       <c r="O12">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="P12">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S12">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>4.9</v>
+        <v>5.16</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
         <v>2.7</v>
@@ -2313,16 +2313,16 @@
         <v>2.22</v>
       </c>
       <c r="AD12">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
         <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2600,22 +2600,22 @@
         <v>2.9</v>
       </c>
       <c r="Q14">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U14">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2624,22 +2624,22 @@
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z14">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AB14">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC14">
         <v>4.75</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE14">
         <v>1.03</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2769,10 +2769,10 @@
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
         <v>2.4</v>
@@ -2781,7 +2781,7 @@
         <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -2793,7 +2793,7 @@
         <v>3.84</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
@@ -2811,7 +2811,7 @@
         <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="P21">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="Q21">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R21">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,13 +3753,13 @@
         <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
         <v>1.03</v>
@@ -3771,16 +3771,16 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AB21">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AD21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Q24">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
         <v>1.41</v>
@@ -4242,7 +4242,7 @@
         <v>2.64</v>
       </c>
       <c r="U24">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="V24">
         <v>1.35</v>
@@ -4251,22 +4251,22 @@
         <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
         <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC24">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4275,7 +4275,7 @@
         <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG24">
         <v>1.8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
         <v>1.62</v>
@@ -4411,10 +4411,10 @@
         <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.14</v>
@@ -4423,10 +4423,10 @@
         <v>5.25</v>
       </c>
       <c r="AA25">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AC25">
         <v>2.43</v>
@@ -4435,7 +4435,7 @@
         <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
         <v>2.35</v>
@@ -4728,7 +4728,7 @@
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="U27">
         <v>2.75</v>
@@ -4743,10 +4743,10 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
         <v>1.82</v>
@@ -4755,16 +4755,16 @@
         <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD27">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
         <v>1.82</v>
@@ -4882,22 +4882,22 @@
         <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R28">
         <v>1.76</v>
       </c>
       <c r="S28">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="T28">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U28">
         <v>4.7</v>
       </c>
       <c r="V28">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="W28">
         <v>1.02</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK28">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5054,10 +5054,10 @@
         <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="U29">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="V29">
         <v>1.36</v>
@@ -5878,7 +5878,7 @@
         <v>1.61</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5896,7 +5896,7 @@
         <v>2.4</v>
       </c>
       <c r="AC34">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AD34">
         <v>1.62</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
         <v>3.7</v>
@@ -6023,22 +6023,22 @@
         <v>5.56</v>
       </c>
       <c r="Q35">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>4.91</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P36">
         <v>1.57</v>
@@ -6189,16 +6189,16 @@
         <v>5.05</v>
       </c>
       <c r="R36">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="S36">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
         <v>1.56</v>
@@ -6222,13 +6222,13 @@
         <v>2.26</v>
       </c>
       <c r="AC36">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD36">
         <v>1.5</v>
       </c>
       <c r="AE36">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
         <v>1.59</v>
@@ -6250,7 +6250,7 @@
         <v>2.25</v>
       </c>
       <c r="AK36">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,19 +6349,19 @@
         <v>2.7</v>
       </c>
       <c r="Q37">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="R37">
         <v>2.11</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
         <v>3</v>
       </c>
       <c r="U37">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
         <v>1.36</v>
@@ -6397,7 +6397,7 @@
         <v>1.71</v>
       </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O39">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="P39">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="Q39">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R39">
         <v>2.1</v>
@@ -6684,7 +6684,7 @@
         <v>1.42</v>
       </c>
       <c r="T39">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="U39">
         <v>2.99</v>
@@ -6708,19 +6708,19 @@
         <v>2.12</v>
       </c>
       <c r="AB39">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE39">
         <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
         <v>1.89</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
+        <v>1.44</v>
+      </c>
+      <c r="AK39">
         <v>1.35</v>
-      </c>
-      <c r="AK39">
-        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O40">
         <v>3.1</v>
@@ -6838,55 +6838,55 @@
         <v>2.72</v>
       </c>
       <c r="Q40">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="R40">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T40">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U40">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
         <v>1.4</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z40">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA40">
         <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC40">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD40">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE40">
         <v>1.07</v>
       </c>
       <c r="AF40">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>4.1</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S41">
         <v>1.3</v>
@@ -7034,10 +7034,10 @@
         <v>1.74</v>
       </c>
       <c r="AB41">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AC41">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AD41">
         <v>1.34</v>
@@ -7327,7 +7327,7 @@
         <v>2.97</v>
       </c>
       <c r="Q43">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R43">
         <v>2.27</v>
@@ -7345,7 +7345,7 @@
         <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK43">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7487,58 +7487,58 @@
         <v>3.1</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R44">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T44">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U44">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA44">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AB44">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC44">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="O45">
+        <v>3.2</v>
+      </c>
+      <c r="P45">
         <v>3.4</v>
       </c>
-      <c r="P45">
-        <v>4.1</v>
-      </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U45">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V45">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7677,31 +7677,31 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB45">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="O46">
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q46">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R46">
         <v>2.2</v>
@@ -7831,7 +7831,7 @@
         <v>2.56</v>
       </c>
       <c r="V46">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W46">
         <v>1.07</v>
@@ -7846,7 +7846,7 @@
         <v>3.9</v>
       </c>
       <c r="AA46">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB46">
         <v>2.1</v>
@@ -7861,7 +7861,7 @@
         <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
         <v>2.25</v>
@@ -7973,7 +7973,7 @@
         <v>2.35</v>
       </c>
       <c r="O47">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P47">
         <v>3.1</v>
@@ -8015,7 +8015,7 @@
         <v>1.68</v>
       </c>
       <c r="AC47">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD47">
         <v>1.23</v>
@@ -8027,7 +8027,7 @@
         <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK47">
         <v>1.56</v>
@@ -8812,7 +8812,7 @@
         <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.04</v>
@@ -8824,7 +8824,7 @@
         <v>3.04</v>
       </c>
       <c r="AA52">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AB52">
         <v>1.66</v>
@@ -8836,7 +8836,7 @@
         <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
         <v>1.77</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
         <v>1.4</v>
@@ -8954,10 +8954,10 @@
         <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q53">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8966,7 +8966,7 @@
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U53">
         <v>2.88</v>
@@ -8975,25 +8975,25 @@
         <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z53">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA53">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB53">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC53">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="AD53">
         <v>1.28</v>
@@ -9005,7 +9005,7 @@
         <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9280,13 +9280,13 @@
         <v>3.3</v>
       </c>
       <c r="P55">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q55">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="R55">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S55">
         <v>1.36</v>
@@ -9295,16 +9295,16 @@
         <v>2.62</v>
       </c>
       <c r="U55">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.28</v>
@@ -9313,25 +9313,25 @@
         <v>3.2</v>
       </c>
       <c r="AA55">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB55">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC55">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD55">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG55">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK55">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.78</v>
+        <v>2.25</v>
       </c>
       <c r="O57">
+        <v>2.74</v>
+      </c>
+      <c r="P57">
+        <v>3.43</v>
+      </c>
+      <c r="Q57">
         <v>3</v>
       </c>
-      <c r="P57">
-        <v>2.78</v>
-      </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
       <c r="R57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O62">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P62">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y62">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Z62">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q64">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -1133,10 +1133,10 @@
         <v>5.9</v>
       </c>
       <c r="Q5">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
         <v>1.33</v>
@@ -1151,10 +1151,10 @@
         <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1.23</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>3.24</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
         <v>1.1</v>
@@ -2467,7 +2467,7 @@
         <v>3.95</v>
       </c>
       <c r="AA13">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
         <v>2.05</v>
@@ -2485,7 +2485,7 @@
         <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="Q16">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2938,10 +2938,10 @@
         <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2956,10 +2956,10 @@
         <v>3.2</v>
       </c>
       <c r="AA16">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
         <v>3.28</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S17">
         <v>1.25</v>
@@ -3107,10 +3107,10 @@
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.11</v>
@@ -3119,7 +3119,7 @@
         <v>4.9</v>
       </c>
       <c r="AA17">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AB17">
         <v>2.37</v>
@@ -3128,10 +3128,10 @@
         <v>2.25</v>
       </c>
       <c r="AD17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF17">
         <v>1.44</v>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P19">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V21">
         <v>1.63</v>
@@ -3768,19 +3768,19 @@
         <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA21">
+        <v>1.53</v>
+      </c>
+      <c r="AB21">
+        <v>2.35</v>
+      </c>
+      <c r="AC21">
+        <v>2.31</v>
+      </c>
+      <c r="AD21">
         <v>1.56</v>
-      </c>
-      <c r="AB21">
-        <v>2.4</v>
-      </c>
-      <c r="AC21">
-        <v>2.29</v>
-      </c>
-      <c r="AD21">
-        <v>1.57</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -4550,7 +4550,7 @@
         <v>3.6</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
         <v>1.95</v>
@@ -4580,10 +4580,10 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
         <v>1.7</v>
@@ -4592,19 +4592,19 @@
         <v>1.99</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE26">
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG26">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -5214,16 +5214,16 @@
         <v>2.27</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
         <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
         <v>1.11</v>
@@ -5238,7 +5238,7 @@
         <v>4.95</v>
       </c>
       <c r="AA30">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB30">
         <v>2.35</v>
@@ -5256,7 +5256,7 @@
         <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O31">
         <v>5</v>
       </c>
       <c r="P31">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5534,13 +5534,13 @@
         <v>4.22</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
         <v>2.87</v>
@@ -5552,28 +5552,28 @@
         <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="AA32">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC32">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
         <v>1.09</v>
@@ -5582,7 +5582,7 @@
         <v>1.68</v>
       </c>
       <c r="AG32">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R33">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="S33">
         <v>1.22</v>
@@ -5739,10 +5739,10 @@
         <v>1.47</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
         <v>1.84</v>
@@ -5863,7 +5863,7 @@
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
         <v>1.2</v>
@@ -5890,16 +5890,16 @@
         <v>5.2</v>
       </c>
       <c r="AA34">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC34">
         <v>2.16</v>
       </c>
       <c r="AD34">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE34">
         <v>1.2</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P38">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB38">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="O40">
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="Q40">
-        <v>3.27</v>
+        <v>2.91</v>
       </c>
       <c r="R40">
         <v>2.04</v>
@@ -6871,7 +6871,7 @@
         <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
         <v>3.28</v>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7167,19 +7167,19 @@
         <v>3.2</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T42">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U42">
         <v>3.3</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W42">
         <v>1.04</v>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8142,25 +8142,25 @@
         <v>2.07</v>
       </c>
       <c r="Q48">
+        <v>3.5</v>
+      </c>
+      <c r="R48">
+        <v>2.24</v>
+      </c>
+      <c r="S48">
+        <v>1.25</v>
+      </c>
+      <c r="T48">
         <v>3.6</v>
       </c>
-      <c r="R48">
-        <v>2.3</v>
-      </c>
-      <c r="S48">
-        <v>1.29</v>
-      </c>
-      <c r="T48">
-        <v>3.3</v>
-      </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V48">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8175,7 +8175,7 @@
         <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AC48">
         <v>2.53</v>
@@ -8190,7 +8190,7 @@
         <v>1.54</v>
       </c>
       <c r="AG48">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="R49">
         <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U49">
         <v>2.6</v>
       </c>
       <c r="V49">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB49">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AC49">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AD49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="O54">
         <v>3.4</v>
       </c>
       <c r="P54">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="R54">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="S54">
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="U54">
         <v>2.77</v>
@@ -9138,13 +9138,13 @@
         <v>1.37</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z54">
         <v>3.19</v>
@@ -9153,13 +9153,13 @@
         <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC54">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AD54">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE54">
         <v>1.05</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK54">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9443,13 +9443,13 @@
         <v>3.9</v>
       </c>
       <c r="P56">
-        <v>6.54</v>
+        <v>5.45</v>
       </c>
       <c r="Q56">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
         <v>1.31</v>
@@ -9482,19 +9482,19 @@
         <v>1.92</v>
       </c>
       <c r="AC56">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD56">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE56">
         <v>1.15</v>
       </c>
       <c r="AF56">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG56">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9615,16 +9615,16 @@
         <v>1.83</v>
       </c>
       <c r="S57">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T57">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U57">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V57">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W57">
         <v>1.03</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10089,28 +10089,28 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O60">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q60">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="R60">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S60">
         <v>1.3</v>
       </c>
       <c r="T60">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U60">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V60">
         <v>1.44</v>
@@ -10125,16 +10125,16 @@
         <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="AA60">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB60">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC60">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AD60">
         <v>1.33</v>
@@ -10146,7 +10146,7 @@
         <v>1.65</v>
       </c>
       <c r="AG60">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.21</v>
       </c>
       <c r="AK60">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10264,7 +10264,7 @@
         <v>1.25</v>
       </c>
       <c r="R61">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="S61">
         <v>1.11</v>
@@ -10273,13 +10273,13 @@
         <v>5.5</v>
       </c>
       <c r="U61">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="V61">
         <v>2.3</v>
       </c>
       <c r="W61">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         <v>1.01</v>
       </c>
       <c r="Z61">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA61">
         <v>1.19</v>
@@ -10309,7 +10309,7 @@
         <v>2.01</v>
       </c>
       <c r="AG61">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK61">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10433,7 +10433,7 @@
         <v>1.62</v>
       </c>
       <c r="T62">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="U62">
         <v>3.95</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>3.5</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
         <v>2.09</v>
@@ -10934,19 +10934,19 @@
         <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA65">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AB65">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC65">
         <v>3.14</v>
@@ -10955,10 +10955,10 @@
         <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG65">
         <v>2</v>
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="O66">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P66">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q66">
         <v>1.79</v>
       </c>
       <c r="R66">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S66">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T66">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="U66">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
         <v>1.08</v>
@@ -11100,31 +11100,31 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AA66">
         <v>1.9</v>
       </c>
       <c r="AB66">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC66">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AD66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
         <v>2.26</v>
       </c>
       <c r="AG66">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK66">
         <v>3.05</v>
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
         <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="V67">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z67">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA67">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC67">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD67">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
+        <v>1.57</v>
+      </c>
+      <c r="AG67">
+        <v>2.2</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.3</v>
+      </c>
+      <c r="AK67">
         <v>1.62</v>
-      </c>
-      <c r="AG67">
-        <v>2.15</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.25</v>
-      </c>
-      <c r="AK67">
-        <v>1.8</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,31 +11393,31 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="O68">
         <v>3.25</v>
       </c>
       <c r="P68">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q68">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R68">
         <v>2</v>
       </c>
       <c r="S68">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T68">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U68">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W68">
         <v>1.02</v>
@@ -11426,31 +11426,31 @@
         <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z68">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AA68">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AB68">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC68">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AD68">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF68">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG68">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -9117,7 +9117,7 @@
         <v>3.4</v>
       </c>
       <c r="P54">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q54">
         <v>2.29</v>
@@ -9283,7 +9283,7 @@
         <v>4.33</v>
       </c>
       <c r="Q55">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R55">
         <v>2.11</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10925,10 +10925,10 @@
         <v>3</v>
       </c>
       <c r="U65">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V65">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W65">
         <v>1.06</v>
@@ -10943,7 +10943,7 @@
         <v>3.5</v>
       </c>
       <c r="AA65">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB65">
         <v>1.83</v>
@@ -11239,7 +11239,7 @@
         <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
         <v>2.25</v>
@@ -11251,13 +11251,13 @@
         <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V67">
         <v>1.45</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11411,7 +11411,7 @@
         <v>1.49</v>
       </c>
       <c r="T68">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U68">
         <v>3.22</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O49">
         <v>3.5</v>
@@ -8305,7 +8305,7 @@
         <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
         <v>2.2</v>
@@ -8335,10 +8335,10 @@
         <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
         <v>2.9</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK57">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>2.65</v>
       </c>
       <c r="Q62">
-        <v>3.94</v>
+        <v>3.32</v>
       </c>
       <c r="R62">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S62">
         <v>1.62</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="O64">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10925,10 +10925,10 @@
         <v>3</v>
       </c>
       <c r="U65">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="V65">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W65">
         <v>1.06</v>
@@ -10940,13 +10940,13 @@
         <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA65">
+        <v>1.94</v>
+      </c>
+      <c r="AB65">
         <v>1.9</v>
-      </c>
-      <c r="AB65">
-        <v>1.83</v>
       </c>
       <c r="AC65">
         <v>3.14</v>
@@ -10955,7 +10955,7 @@
         <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
         <v>1.75</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O67">
         <v>3.6</v>
@@ -11239,7 +11239,7 @@
         <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R67">
         <v>2.25</v>
@@ -11251,13 +11251,13 @@
         <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V67">
         <v>1.45</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11269,7 +11269,7 @@
         <v>4.1</v>
       </c>
       <c r="AA67">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB67">
         <v>2.1</v>
@@ -11284,7 +11284,7 @@
         <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG67">
         <v>2.2</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
         <v>3.34</v>
@@ -807,7 +807,7 @@
         <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R3">
         <v>2.06</v>
@@ -837,7 +837,7 @@
         <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AB3">
         <v>1.88</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>2.49</v>
+        <v>2.73</v>
       </c>
       <c r="P8">
         <v>2.61</v>
@@ -1640,10 +1640,10 @@
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y8">
         <v>1.53</v>
@@ -1800,10 +1800,10 @@
         <v>3.6</v>
       </c>
       <c r="V9">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.07</v>
@@ -1830,10 +1830,10 @@
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         <v>1.6</v>
       </c>
       <c r="Q10">
-        <v>5.41</v>
+        <v>4.41</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
         <v>3.1</v>
@@ -1963,7 +1963,7 @@
         <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.07</v>
@@ -1978,10 +1978,10 @@
         <v>3.71</v>
       </c>
       <c r="AA10">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
         <v>2.98</v>
@@ -1990,13 +1990,13 @@
         <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O11">
         <v>3.25</v>
@@ -2277,13 +2277,13 @@
         <v>1.53</v>
       </c>
       <c r="R12">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="S12">
         <v>1.18</v>
       </c>
       <c r="T12">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
         <v>2.22</v>
@@ -2301,28 +2301,28 @@
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>5.16</v>
+        <v>5.75</v>
       </c>
       <c r="AA12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB12">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC12">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AD12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE12">
         <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="O15">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="Q15">
+        <v>2.15</v>
+      </c>
+      <c r="R15">
         <v>2.38</v>
-      </c>
-      <c r="R15">
-        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.29</v>
@@ -2787,31 +2787,31 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
         <v>1.33</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O19">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,43 +3569,43 @@
         </is>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="O20">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P20">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA20">
         <v>1.53</v>
@@ -3614,19 +3614,19 @@
         <v>2.37</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         <v>3.53</v>
       </c>
       <c r="P21">
-        <v>2.71</v>
+        <v>2.27</v>
       </c>
       <c r="Q21">
         <v>2.8</v>
       </c>
       <c r="R21">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,10 +3753,10 @@
         <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="V21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3765,7 +3765,7 @@
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
         <v>4.95</v>
@@ -3774,13 +3774,13 @@
         <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
         <v>2.31</v>
       </c>
       <c r="AD21">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3789,7 +3789,7 @@
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4079,13 +4079,13 @@
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4097,13 +4097,13 @@
         <v>3.84</v>
       </c>
       <c r="AA23">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC23">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
@@ -4131,7 +4131,7 @@
         <v>1.14</v>
       </c>
       <c r="AK23">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
         <v>2.96</v>
@@ -4260,10 +4260,10 @@
         <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
         <v>4.07</v>
@@ -4387,13 +4387,13 @@
         <v>1.45</v>
       </c>
       <c r="O25">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q25">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
         <v>2.4</v>
@@ -4411,22 +4411,22 @@
         <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="AC25">
         <v>2.43</v>
@@ -4435,13 +4435,13 @@
         <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="P26">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -4562,19 +4562,19 @@
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V26">
         <v>1.48</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4586,10 +4586,10 @@
         <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
         <v>2.73</v>
@@ -4601,10 +4601,10 @@
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>3.05</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4743,22 +4743,22 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="AA27">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
         <v>3.04</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
         <v>1.11</v>
@@ -4876,7 +4876,7 @@
         <v>2.15</v>
       </c>
       <c r="O28">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="P28">
         <v>3.7</v>
@@ -4888,7 +4888,7 @@
         <v>1.76</v>
       </c>
       <c r="S28">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="T28">
         <v>2.1</v>
@@ -4897,7 +4897,7 @@
         <v>4.7</v>
       </c>
       <c r="V28">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="W28">
         <v>1.02</v>
@@ -4912,10 +4912,10 @@
         <v>1.98</v>
       </c>
       <c r="AA28">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AB28">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AC28">
         <v>7.6</v>
@@ -5051,19 +5051,19 @@
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
         <v>2.81</v>
       </c>
       <c r="U29">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V29">
         <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5078,7 +5078,7 @@
         <v>2.07</v>
       </c>
       <c r="AB29">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="O34">
         <v>4.25</v>
@@ -5860,16 +5860,16 @@
         <v>4.2</v>
       </c>
       <c r="Q34">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
         <v>2.19</v>
@@ -5878,7 +5878,7 @@
         <v>1.61</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5890,13 +5890,13 @@
         <v>5.2</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD34">
         <v>1.66</v>
@@ -5905,7 +5905,7 @@
         <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
         <v>2.31</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O35">
         <v>3.7</v>
@@ -6032,10 +6032,10 @@
         <v>1.37</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
         <v>1.41</v>
@@ -6053,7 +6053,7 @@
         <v>3.2</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB35">
         <v>1.85</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
         <v>2.28</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.91</v>
+        <v>4.33</v>
       </c>
       <c r="O36">
         <v>4</v>
       </c>
       <c r="P36">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q36">
         <v>5.05</v>
@@ -6198,16 +6198,16 @@
         <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V36">
         <v>1.56</v>
       </c>
       <c r="W36">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.12</v>
@@ -6219,22 +6219,22 @@
         <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC36">
         <v>2.4</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
         <v>1.21</v>
       </c>
       <c r="AF36">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>2.21</v>
       </c>
       <c r="Q39">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R39">
         <v>2.1</v>
@@ -6714,16 +6714,16 @@
         <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
         <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6844,19 +6844,19 @@
         <v>2.04</v>
       </c>
       <c r="S40">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6886,7 +6886,7 @@
         <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>2.21</v>
@@ -7031,7 +7031,7 @@
         <v>3.58</v>
       </c>
       <c r="AA41">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
         <v>2.03</v>
@@ -7046,10 +7046,10 @@
         <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7155,34 +7155,34 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="O42">
         <v>3.05</v>
       </c>
       <c r="P42">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="Q42">
+        <v>3</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="S42">
+        <v>1.4</v>
+      </c>
+      <c r="T42">
+        <v>2.6</v>
+      </c>
+      <c r="U42">
         <v>3.2</v>
       </c>
-      <c r="R42">
-        <v>1.91</v>
-      </c>
-      <c r="S42">
-        <v>1.45</v>
-      </c>
-      <c r="T42">
-        <v>2.55</v>
-      </c>
-      <c r="U42">
-        <v>3.3</v>
-      </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>2.97</v>
       </c>
       <c r="Q43">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="R43">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AB43">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AC43">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AD43">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>1.37</v>
       </c>
       <c r="T44">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="U44">
         <v>2.77</v>
@@ -7535,10 +7535,10 @@
         <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O45">
         <v>3.2</v>
@@ -7665,10 +7665,10 @@
         <v>2.65</v>
       </c>
       <c r="U45">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7686,7 +7686,7 @@
         <v>1.96</v>
       </c>
       <c r="AB45">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
         <v>3.34</v>
@@ -7701,7 +7701,7 @@
         <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O46">
         <v>3.5</v>
@@ -7828,7 +7828,7 @@
         <v>3.12</v>
       </c>
       <c r="U46">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
         <v>1.49</v>
@@ -7988,7 +7988,7 @@
         <v>1.44</v>
       </c>
       <c r="T47">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="U47">
         <v>2.88</v>
@@ -8009,7 +8009,7 @@
         <v>2.82</v>
       </c>
       <c r="AA47">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB47">
         <v>1.68</v>
@@ -8151,16 +8151,16 @@
         <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8172,7 +8172,7 @@
         <v>4.3</v>
       </c>
       <c r="AA48">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB48">
         <v>2.23</v>
@@ -8206,7 +8206,7 @@
         <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="O52">
         <v>3</v>
@@ -8827,7 +8827,7 @@
         <v>2.16</v>
       </c>
       <c r="AB52">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC52">
         <v>3.9</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O53">
         <v>3.25</v>
@@ -9114,28 +9114,28 @@
         <v>1.57</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P54">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q54">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="R54">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S54">
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U54">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V54">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
         <v>1.05</v>
@@ -9150,7 +9150,7 @@
         <v>3.19</v>
       </c>
       <c r="AA54">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB54">
         <v>1.75</v>
@@ -9184,7 +9184,7 @@
         <v>1.15</v>
       </c>
       <c r="AK54">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>2.38</v>
       </c>
       <c r="R55">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="S55">
         <v>1.36</v>
@@ -9313,10 +9313,10 @@
         <v>3.2</v>
       </c>
       <c r="AA55">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB55">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC55">
         <v>3.34</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11070,22 +11070,22 @@
         <v>1.2</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P66">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Q66">
         <v>1.79</v>
       </c>
       <c r="R66">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="S66">
         <v>1.34</v>
       </c>
       <c r="T66">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U66">
         <v>2.75</v>
@@ -11106,10 +11106,10 @@
         <v>3.28</v>
       </c>
       <c r="AA66">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB66">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC66">
         <v>3.18</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK66">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
         <v>3.5</v>
       </c>
       <c r="Q68">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S68">
         <v>1.49</v>
       </c>
       <c r="T68">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U68">
         <v>3.22</v>
@@ -11432,13 +11432,13 @@
         <v>2.83</v>
       </c>
       <c r="AA68">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AB68">
         <v>1.57</v>
       </c>
       <c r="AC68">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD68">
         <v>1.21</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
         <v>1.73</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -2458,7 +2458,7 @@
         <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
         <v>1.17</v>
@@ -2467,7 +2467,7 @@
         <v>3.95</v>
       </c>
       <c r="AA13">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
         <v>2.05</v>
@@ -2959,7 +2959,7 @@
         <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
         <v>3.28</v>
@@ -5205,16 +5205,16 @@
         <v>3.6</v>
       </c>
       <c r="P30">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="R30">
         <v>2.27</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
         <v>3.6</v>
@@ -5238,7 +5238,7 @@
         <v>4.95</v>
       </c>
       <c r="AA30">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB30">
         <v>2.35</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
         <v>1.4</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
         <v>4.22</v>
@@ -5564,7 +5564,7 @@
         <v>3.84</v>
       </c>
       <c r="AA32">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
         <v>2.08</v>
@@ -5579,7 +5579,7 @@
         <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
         <v>2.1</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
         <v>7</v>
@@ -5700,7 +5700,7 @@
         <v>1.78</v>
       </c>
       <c r="R33">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="S33">
         <v>1.22</v>
@@ -5730,7 +5730,7 @@
         <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
         <v>2.35</v>
@@ -5761,7 +5761,7 @@
         <v>1.12</v>
       </c>
       <c r="AK33">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O38">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="O49">
         <v>3.5</v>
@@ -8338,7 +8338,7 @@
         <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC49">
         <v>2.9</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
         <v>1.43</v>
@@ -8498,7 +8498,7 @@
         <v>5.25</v>
       </c>
       <c r="AA50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
         <v>2.56</v>
@@ -8631,7 +8631,7 @@
         <v>3.06</v>
       </c>
       <c r="Q51">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R51">
         <v>2.3</v>
@@ -8658,7 +8658,7 @@
         <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
         <v>1.76</v>
@@ -8679,7 +8679,7 @@
         <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.23</v>
@@ -9494,7 +9494,7 @@
         <v>1.85</v>
       </c>
       <c r="AG56">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB58">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -10110,7 +10110,7 @@
         <v>3.2</v>
       </c>
       <c r="U60">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V60">
         <v>1.44</v>
@@ -10122,7 +10122,7 @@
         <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z60">
         <v>4.05</v>
@@ -10131,22 +10131,22 @@
         <v>1.7</v>
       </c>
       <c r="AB60">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF60">
         <v>1.65</v>
       </c>
       <c r="AG60">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK60">
         <v>1.83</v>
@@ -10291,10 +10291,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AA61">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AB61">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="AC61">
         <v>1.53</v>
@@ -10306,10 +10306,10 @@
         <v>1.58</v>
       </c>
       <c r="AF61">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AG61">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK61">
         <v>9</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="O64">
         <v>3.2</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P65">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q65">
         <v>3.7</v>
@@ -10925,19 +10925,19 @@
         <v>3</v>
       </c>
       <c r="U65">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="V65">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W65">
         <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z65">
         <v>3.4</v>
@@ -10946,16 +10946,16 @@
         <v>1.94</v>
       </c>
       <c r="AB65">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC65">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD65">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
         <v>1.75</v>
@@ -11269,10 +11269,10 @@
         <v>4.1</v>
       </c>
       <c r="AA67">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB67">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC67">
         <v>2.75</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -6355,13 +6355,13 @@
         <v>2.11</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
         <v>3</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="V37">
         <v>1.36</v>
@@ -6397,7 +6397,7 @@
         <v>1.71</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="O64">
         <v>3.2</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -1954,7 +1954,7 @@
         <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
         <v>3.1</v>
@@ -2458,7 +2458,7 @@
         <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.17</v>
@@ -2485,7 +2485,7 @@
         <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         <v>3.55</v>
       </c>
       <c r="O26">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="P26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -4568,7 +4568,7 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
         <v>1.48</v>
@@ -4580,7 +4580,7 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z26">
         <v>4.1</v>
@@ -4595,7 +4595,7 @@
         <v>2.73</v>
       </c>
       <c r="AD26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
         <v>1.16</v>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U29">
         <v>2.8</v>
@@ -5075,10 +5075,10 @@
         <v>2.92</v>
       </c>
       <c r="AA29">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB29">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB31">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -8157,7 +8157,7 @@
         <v>2.3</v>
       </c>
       <c r="V48">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W48">
         <v>1.1</v>
@@ -8187,7 +8187,7 @@
         <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG48">
         <v>2.32</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O54">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q54">
         <v>2.35</v>
@@ -9129,7 +9129,7 @@
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U54">
         <v>2.9</v>
@@ -9147,22 +9147,22 @@
         <v>1.34</v>
       </c>
       <c r="Z54">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AA54">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AB54">
         <v>1.75</v>
       </c>
       <c r="AC54">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="AD54">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE54">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
         <v>1.91</v>
@@ -9446,7 +9446,7 @@
         <v>5.45</v>
       </c>
       <c r="Q56">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="R56">
         <v>2.3</v>
@@ -9458,7 +9458,7 @@
         <v>3.26</v>
       </c>
       <c r="U56">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="V56">
         <v>1.44</v>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10098,7 +10098,7 @@
         <v>3.35</v>
       </c>
       <c r="Q60">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R60">
         <v>2.24</v>
@@ -10110,7 +10110,7 @@
         <v>3.2</v>
       </c>
       <c r="U60">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V60">
         <v>1.44</v>
@@ -10590,7 +10590,7 @@
         <v>1.36</v>
       </c>
       <c r="R63">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="S63">
         <v>1.18</v>
@@ -10599,7 +10599,7 @@
         <v>4.8</v>
       </c>
       <c r="U63">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V63">
         <v>1.89</v>
@@ -10626,13 +10626,13 @@
         <v>1.74</v>
       </c>
       <c r="AD63">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AE63">
         <v>1.41</v>
       </c>
       <c r="AF63">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG63">
         <v>1.57</v>
@@ -11070,10 +11070,10 @@
         <v>1.2</v>
       </c>
       <c r="O66">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P66">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q66">
         <v>1.79</v>
@@ -11085,10 +11085,10 @@
         <v>1.34</v>
       </c>
       <c r="T66">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U66">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V66">
         <v>1.44</v>
@@ -11103,13 +11103,13 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA66">
         <v>1.89</v>
       </c>
       <c r="AB66">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC66">
         <v>3.18</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O68">
         <v>3.2</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -2609,7 +2609,7 @@
         <v>1.49</v>
       </c>
       <c r="T14">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U14">
         <v>3.38</v>
@@ -2630,7 +2630,7 @@
         <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AB14">
         <v>1.57</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK14">
         <v>1.37</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
         <v>3.7</v>
       </c>
       <c r="P15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
         <v>2.15</v>
@@ -2793,10 +2793,10 @@
         <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
         <v>2.49</v>
@@ -4067,55 +4067,55 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q23">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T23">
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB23">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.14</v>
       </c>
       <c r="AK23">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4405,25 +4405,25 @@
         <v>3.26</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W25">
         <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
         <v>2.34</v>
@@ -4435,7 +4435,7 @@
         <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
@@ -4580,7 +4580,7 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
         <v>4.1</v>
@@ -4592,13 +4592,13 @@
         <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
         <v>1.67</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="O35">
         <v>3.7</v>
@@ -6023,55 +6023,55 @@
         <v>5.56</v>
       </c>
       <c r="Q35">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V35">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="AA35">
         <v>1.9</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK35">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O40">
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q40">
         <v>2.91</v>
@@ -6859,13 +6859,13 @@
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA40">
         <v>1.9</v>
@@ -6874,19 +6874,19 @@
         <v>1.8</v>
       </c>
       <c r="AC40">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
         <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T47">
         <v>2.8</v>
@@ -7997,7 +7997,7 @@
         <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.04</v>
@@ -8006,16 +8006,16 @@
         <v>1.34</v>
       </c>
       <c r="Z47">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AA47">
         <v>2.1</v>
       </c>
       <c r="AB47">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC47">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD47">
         <v>1.23</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK47">
         <v>1.56</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -807,7 +807,7 @@
         <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="R3">
         <v>2.06</v>
@@ -816,7 +816,7 @@
         <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
         <v>2.75</v>
@@ -834,22 +834,22 @@
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
         <v>1.88</v>
       </c>
       <c r="AC3">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AD3">
         <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
         <v>1.7</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
         <v>1.79</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P5">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AG5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O8">
         <v>2.73</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
         <v>1.53</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="O9">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="P9">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -1797,7 +1797,7 @@
         <v>2.38</v>
       </c>
       <c r="U9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -1806,28 +1806,28 @@
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z9">
         <v>2.39</v>
       </c>
       <c r="AA9">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AB9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC9">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="AD9">
         <v>1.13</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
         <v>2.2</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q10">
         <v>4.41</v>
@@ -1954,7 +1954,7 @@
         <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
         <v>3.1</v>
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q11">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="R11">
         <v>2.01</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
         <v>2.7</v>
@@ -2135,31 +2135,31 @@
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA11">
         <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD11">
         <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="O12">
         <v>5.9</v>
@@ -2280,19 +2280,19 @@
         <v>2.8</v>
       </c>
       <c r="S12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
         <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V12">
         <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2301,28 +2301,28 @@
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA12">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB12">
         <v>2.6</v>
       </c>
       <c r="AC12">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P14">
         <v>2.9</v>
@@ -2920,7 +2920,7 @@
         <v>2.93</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
         <v>2.13</v>
@@ -2947,13 +2947,13 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA16">
         <v>1.9</v>
@@ -2962,16 +2962,16 @@
         <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
         <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
         <v>2</v>
@@ -3086,22 +3086,22 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R17">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
         <v>1.62</v>
@@ -3110,7 +3110,7 @@
         <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.11</v>
@@ -3119,25 +3119,25 @@
         <v>4.9</v>
       </c>
       <c r="AA17">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AB17">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AC17">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD17">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF17">
         <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O21">
         <v>3.53</v>
@@ -3744,10 +3744,10 @@
         <v>2.8</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
         <v>3.8</v>
@@ -3762,7 +3762,7 @@
         <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.14</v>
@@ -3771,7 +3771,7 @@
         <v>4.95</v>
       </c>
       <c r="AA21">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
         <v>2.33</v>
@@ -3789,7 +3789,7 @@
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>1.64</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
         <v>2.52</v>
@@ -4242,7 +4242,7 @@
         <v>2.64</v>
       </c>
       <c r="U24">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V24">
         <v>1.35</v>
@@ -4251,7 +4251,7 @@
         <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
         <v>1.31</v>
@@ -4260,7 +4260,7 @@
         <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
         <v>1.65</v>
@@ -4294,7 +4294,7 @@
         <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>1.5</v>
       </c>
       <c r="O27">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P27">
         <v>4.65</v>
@@ -4728,7 +4728,7 @@
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U27">
         <v>2.6</v>
@@ -4737,16 +4737,16 @@
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
         <v>1.87</v>
@@ -4755,16 +4755,16 @@
         <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD27">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG27">
         <v>1.82</v>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>2.15</v>
       </c>
       <c r="O28">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="P28">
         <v>3.7</v>
@@ -4885,7 +4885,7 @@
         <v>3</v>
       </c>
       <c r="R28">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S28">
         <v>1.74</v>
@@ -4894,43 +4894,43 @@
         <v>2.1</v>
       </c>
       <c r="U28">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="V28">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Y28">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Z28">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AA28">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB28">
         <v>1.33</v>
       </c>
       <c r="AC28">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AE28">
         <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AG28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
         <v>1.57</v>
@@ -5087,7 +5087,7 @@
         <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
@@ -5205,10 +5205,10 @@
         <v>3.6</v>
       </c>
       <c r="P30">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q30">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="R30">
         <v>2.27</v>
@@ -5217,7 +5217,7 @@
         <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U30">
         <v>2.2</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
         <v>4.95</v>
@@ -5253,10 +5253,10 @@
         <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG30">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="P32">
         <v>4.22</v>
@@ -5543,7 +5543,7 @@
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
         <v>2.44</v>
@@ -5558,10 +5558,10 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
@@ -5573,10 +5573,10 @@
         <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
         <v>1.67</v>
@@ -5721,7 +5721,7 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
         <v>4.8</v>
@@ -5733,7 +5733,7 @@
         <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
         <v>1.47</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK33">
         <v>3</v>
@@ -5857,25 +5857,25 @@
         <v>4.25</v>
       </c>
       <c r="P34">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
         <v>1.17</v>
@@ -5896,10 +5896,10 @@
         <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE34">
         <v>1.2</v>
@@ -5908,7 +5908,7 @@
         <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
         <v>2.2</v>
@@ -6201,13 +6201,13 @@
         <v>2.32</v>
       </c>
       <c r="V36">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.12</v>
@@ -6216,19 +6216,19 @@
         <v>4.7</v>
       </c>
       <c r="AA36">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD36">
         <v>1.53</v>
       </c>
       <c r="AE36">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
         <v>1.62</v>
@@ -6509,7 +6509,7 @@
         <v>3.6</v>
       </c>
       <c r="P38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O39">
-        <v>3.08</v>
+        <v>3.33</v>
       </c>
       <c r="P39">
         <v>2.21</v>
@@ -6681,13 +6681,13 @@
         <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
         <v>2.69</v>
       </c>
       <c r="U39">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK40">
         <v>1.4</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O41">
         <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q41">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="R41">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
         <v>1.3</v>
@@ -7025,22 +7025,22 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
         <v>3.58</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE41">
         <v>1.1</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,34 +7155,34 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q42">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
         <v>2</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
         <v>2.6</v>
       </c>
       <c r="U42">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7191,7 +7191,7 @@
         <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AA42">
         <v>2.15</v>
@@ -7336,7 +7336,7 @@
         <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U43">
         <v>2.1</v>
@@ -7363,19 +7363,19 @@
         <v>2.46</v>
       </c>
       <c r="AC43">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AD43">
         <v>1.64</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF43">
         <v>1.42</v>
       </c>
       <c r="AG43">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7484,25 +7484,25 @@
         <v>2.15</v>
       </c>
       <c r="O44">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q44">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="R44">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="S44">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U44">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V44">
         <v>1.4</v>
@@ -7511,34 +7511,34 @@
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z44">
         <v>3.25</v>
       </c>
       <c r="AA44">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB44">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC44">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
         <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P45">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q45">
         <v>2.6</v>
@@ -7659,16 +7659,16 @@
         <v>2.1</v>
       </c>
       <c r="S45">
+        <v>1.39</v>
+      </c>
+      <c r="T45">
+        <v>2.61</v>
+      </c>
+      <c r="U45">
+        <v>2.74</v>
+      </c>
+      <c r="V45">
         <v>1.38</v>
-      </c>
-      <c r="T45">
-        <v>2.65</v>
-      </c>
-      <c r="U45">
-        <v>2.73</v>
-      </c>
-      <c r="V45">
-        <v>1.4</v>
       </c>
       <c r="W45">
         <v>1.06</v>
@@ -7683,22 +7683,22 @@
         <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB45">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC45">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD45">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
         <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG45">
         <v>1.85</v>
@@ -7717,7 +7717,7 @@
         <v>1.26</v>
       </c>
       <c r="AK45">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7837,28 +7837,28 @@
         <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB46">
         <v>2.1</v>
       </c>
       <c r="AC46">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD46">
         <v>1.37</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
         <v>1.57</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
         <v>1.44</v>
@@ -7976,7 +7976,7 @@
         <v>3.2</v>
       </c>
       <c r="P47">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="Q47">
         <v>2.8</v>
@@ -8142,13 +8142,13 @@
         <v>2.07</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R48">
         <v>2.24</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.4</v>
@@ -8160,7 +8160,7 @@
         <v>1.53</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O49">
         <v>3.5</v>
@@ -8326,13 +8326,13 @@
         <v>1.08</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
         <v>1.72</v>
@@ -8341,13 +8341,13 @@
         <v>1.98</v>
       </c>
       <c r="AC49">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
@@ -8480,7 +8480,7 @@
         <v>4</v>
       </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V50">
         <v>1.67</v>
@@ -8492,22 +8492,22 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA50">
         <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC50">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD50">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE50">
         <v>1.25</v>
@@ -8788,7 +8788,7 @@
         <v>2.77</v>
       </c>
       <c r="O52">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P52">
         <v>2.45</v>
@@ -8812,16 +8812,16 @@
         <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
         <v>2.16</v>
@@ -8830,7 +8830,7 @@
         <v>1.69</v>
       </c>
       <c r="AC52">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD52">
         <v>1.22</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK52">
         <v>1.4</v>
@@ -8957,7 +8957,7 @@
         <v>2.54</v>
       </c>
       <c r="Q53">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8990,7 +8990,7 @@
         <v>2.08</v>
       </c>
       <c r="AB53">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
         <v>3.66</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>2.38</v>
       </c>
       <c r="R55">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="S55">
         <v>1.36</v>
@@ -9295,22 +9295,22 @@
         <v>2.62</v>
       </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W55">
         <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA55">
         <v>2.03</v>
@@ -9319,10 +9319,10 @@
         <v>1.79</v>
       </c>
       <c r="AC55">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD55">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O56">
         <v>3.9</v>
       </c>
       <c r="P56">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9452,13 +9452,13 @@
         <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="U56">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="V56">
         <v>1.44</v>
@@ -9473,7 +9473,7 @@
         <v>1.23</v>
       </c>
       <c r="Z56">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="AA56">
         <v>1.79</v>
@@ -9615,7 +9615,7 @@
         <v>1.83</v>
       </c>
       <c r="S57">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T57">
         <v>2.2</v>
@@ -9639,7 +9639,7 @@
         <v>2.1</v>
       </c>
       <c r="AA57">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB57">
         <v>1.36</v>
@@ -10101,13 +10101,13 @@
         <v>2.4</v>
       </c>
       <c r="R60">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T60">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U60">
         <v>2.5</v>
@@ -10162,7 +10162,7 @@
         <v>1.19</v>
       </c>
       <c r="AK60">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="O61">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="P61">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="Q61">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="R61">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="S61">
         <v>1.11</v>
@@ -10273,10 +10273,10 @@
         <v>5.5</v>
       </c>
       <c r="U61">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V61">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="W61">
         <v>1.35</v>
@@ -10291,25 +10291,25 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AA61">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB61">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC61">
         <v>1.53</v>
       </c>
       <c r="AD61">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AE61">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF61">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG61">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK61">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,7 +10418,7 @@
         <v>2.8</v>
       </c>
       <c r="O62">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P62">
         <v>2.65</v>
@@ -10427,7 +10427,7 @@
         <v>3.32</v>
       </c>
       <c r="R62">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S62">
         <v>1.62</v>
@@ -10454,7 +10454,7 @@
         <v>2.13</v>
       </c>
       <c r="AA62">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AB62">
         <v>1.3</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O65">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
         <v>2.02</v>
@@ -10940,7 +10940,7 @@
         <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA65">
         <v>1.94</v>
@@ -10977,7 +10977,7 @@
         <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11251,10 +11251,10 @@
         <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V67">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
         <v>1.08</v>
@@ -11263,7 +11263,7 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z67">
         <v>4.1</v>
@@ -11281,10 +11281,10 @@
         <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG67">
         <v>2.2</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
         <v>1.62</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -816,10 +816,10 @@
         <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
         <v>1.41</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
         <v>1.79</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P10">
         <v>1.58</v>
@@ -1960,7 +1960,7 @@
         <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -1975,7 +1975,7 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="AA10">
         <v>1.79</v>
@@ -1984,7 +1984,7 @@
         <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AD10">
         <v>1.36</v>
@@ -2105,10 +2105,10 @@
         <v>2.3</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q11">
         <v>2.94</v>
@@ -2117,7 +2117,7 @@
         <v>2.01</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
         <v>2.7</v>
@@ -2156,7 +2156,7 @@
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
         <v>1.85</v>
@@ -2464,7 +2464,7 @@
         <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA13">
         <v>1.7</v>
@@ -2476,7 +2476,7 @@
         <v>2.62</v>
       </c>
       <c r="AD13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
@@ -2941,7 +2941,7 @@
         <v>2.83</v>
       </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -3409,61 +3409,61 @@
         <v>1.55</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
         <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB19">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P20">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q20">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S20">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
         <v>3.6</v>
       </c>
       <c r="U20">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
         <v>1.62</v>
@@ -3599,7 +3599,7 @@
         <v>1.15</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.12</v>
@@ -3614,10 +3614,10 @@
         <v>2.37</v>
       </c>
       <c r="AC20">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE20">
         <v>1.21</v>
@@ -4230,7 +4230,7 @@
         <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="R24">
         <v>2.05</v>
@@ -4266,7 +4266,7 @@
         <v>1.65</v>
       </c>
       <c r="AC24">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4550,10 +4550,10 @@
         <v>3.55</v>
       </c>
       <c r="O26">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -5368,37 +5368,37 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5407,19 +5407,19 @@
         <v>2.75</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O32">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
         <v>4.22</v>
@@ -5761,7 +5761,7 @@
         <v>1.04</v>
       </c>
       <c r="AK33">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6198,13 +6198,13 @@
         <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6509,7 +6509,7 @@
         <v>3.6</v>
       </c>
       <c r="P38">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
         <v>2.21</v>
@@ -6708,7 +6708,7 @@
         <v>2.12</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="R44">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T44">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U44">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
         <v>3.25</v>
       </c>
       <c r="AA44">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB44">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC44">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD44">
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG44">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="O45">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P45">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q45">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S45">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="U45">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="V45">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
         <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB45">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AD45">
         <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8154,7 +8154,7 @@
         <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
         <v>1.53</v>
@@ -8175,7 +8175,7 @@
         <v>1.71</v>
       </c>
       <c r="AB48">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AC48">
         <v>2.53</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="O49">
         <v>3.5</v>
@@ -8335,7 +8335,7 @@
         <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB49">
         <v>1.98</v>
@@ -8788,7 +8788,7 @@
         <v>2.77</v>
       </c>
       <c r="O52">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
         <v>2.45</v>
@@ -8812,7 +8812,7 @@
         <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
         <v>1.06</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AK52">
         <v>1.4</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,16 +9120,16 @@
         <v>3.5</v>
       </c>
       <c r="Q54">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S54">
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="U54">
         <v>2.9</v>
@@ -9141,28 +9141,28 @@
         <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y54">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z54">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA54">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
         <v>1.75</v>
       </c>
       <c r="AC54">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD54">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF54">
         <v>1.91</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="O56">
         <v>3.9</v>
@@ -9458,7 +9458,7 @@
         <v>3.24</v>
       </c>
       <c r="U56">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="V56">
         <v>1.44</v>
@@ -9772,34 +9772,34 @@
         <v>1.69</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA58">
         <v>1.6</v>
@@ -9808,19 +9808,19 @@
         <v>2.3</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10092,13 +10092,13 @@
         <v>1.85</v>
       </c>
       <c r="O60">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R60">
         <v>2.25</v>
@@ -10113,40 +10113,40 @@
         <v>2.5</v>
       </c>
       <c r="V60">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
         <v>1.11</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB60">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC60">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD60">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
         <v>1.8</v>
@@ -10418,7 +10418,7 @@
         <v>2.8</v>
       </c>
       <c r="O62">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P62">
         <v>2.65</v>
@@ -10430,16 +10430,16 @@
         <v>1.8</v>
       </c>
       <c r="S62">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T62">
         <v>2.11</v>
       </c>
       <c r="U62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="V62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W62">
         <v>1.03</v>
@@ -10596,7 +10596,7 @@
         <v>1.18</v>
       </c>
       <c r="T63">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="U63">
         <v>1.83</v>
@@ -10620,7 +10620,7 @@
         <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC63">
         <v>1.74</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK63">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P64">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>4.5</v>
       </c>
       <c r="P66">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="Q66">
         <v>1.79</v>
@@ -11402,10 +11402,10 @@
         <v>3.5</v>
       </c>
       <c r="Q68">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="R68">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S68">
         <v>1.49</v>
@@ -11423,7 +11423,7 @@
         <v>1.02</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y68">
         <v>1.42</v>
@@ -11444,10 +11444,10 @@
         <v>1.21</v>
       </c>
       <c r="AE68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG68">
         <v>1.75</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
         <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="R3">
         <v>2.06</v>
@@ -819,7 +819,7 @@
         <v>3</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
         <v>1.41</v>
@@ -837,7 +837,7 @@
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AB3">
         <v>1.88</v>
@@ -852,7 +852,7 @@
         <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
         <v>2.06</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
         <v>1.79</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O5">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P5">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="Q5">
         <v>1.96</v>
@@ -1145,7 +1145,7 @@
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1160,13 +1160,13 @@
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>2.78</v>
@@ -1175,10 +1175,10 @@
         <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG5">
         <v>1.8</v>
@@ -1942,10 +1942,10 @@
         <v>4.48</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q10">
         <v>4.41</v>
@@ -1954,7 +1954,7 @@
         <v>2.17</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
         <v>3.1</v>
@@ -1966,16 +1966,16 @@
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="AA10">
         <v>1.79</v>
@@ -1984,10 +1984,10 @@
         <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -2105,7 +2105,7 @@
         <v>2.3</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
         <v>2.96</v>
@@ -2141,7 +2141,7 @@
         <v>2.9</v>
       </c>
       <c r="AA11">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB11">
         <v>1.66</v>
@@ -2268,13 +2268,13 @@
         <v>1.11</v>
       </c>
       <c r="O12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>12.6</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R12">
         <v>2.8</v>
@@ -2286,7 +2286,7 @@
         <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V12">
         <v>1.67</v>
@@ -2298,7 +2298,7 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
         <v>5.4</v>
@@ -2316,13 +2316,13 @@
         <v>1.6</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>3</v>
       </c>
       <c r="P14">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="Q14">
         <v>3.07</v>
@@ -2606,10 +2606,10 @@
         <v>1.92</v>
       </c>
       <c r="S14">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
         <v>3.38</v>
@@ -2618,7 +2618,7 @@
         <v>1.26</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2763,55 +2763,55 @@
         <v>3.7</v>
       </c>
       <c r="Q15">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA15">
         <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC15">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
         <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>2.93</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -2938,7 +2938,7 @@
         <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2956,7 +2956,7 @@
         <v>3.5</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
         <v>1.85</v>
@@ -3083,10 +3083,10 @@
         <v>2.82</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q17">
         <v>3.08</v>
@@ -3101,7 +3101,7 @@
         <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>1.62</v>
@@ -3113,22 +3113,22 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>4.9</v>
+        <v>5.06</v>
       </c>
       <c r="AA17">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AC17">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AD17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE17">
         <v>1.24</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="O21">
         <v>3.53</v>
@@ -3741,25 +3741,25 @@
         <v>2.27</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S21">
         <v>1.19</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
         <v>1.62</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3771,16 +3771,16 @@
         <v>4.95</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
         <v>2.31</v>
       </c>
       <c r="AD21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
         <v>1.53</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P23">
-        <v>9.550000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q23">
         <v>1.81</v>
@@ -4073,7 +4073,7 @@
         <v>2.44</v>
       </c>
       <c r="S23">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
         <v>3.25</v>
@@ -4085,7 +4085,7 @@
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4097,7 +4097,7 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
         <v>2.15</v>
@@ -4224,7 +4224,7 @@
         <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
         <v>3.1</v>
@@ -4233,7 +4233,7 @@
         <v>2.95</v>
       </c>
       <c r="R24">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="S24">
         <v>1.41</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK24">
         <v>1.64</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="O25">
         <v>4</v>
@@ -4393,25 +4393,25 @@
         <v>5.75</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R25">
         <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>3.26</v>
       </c>
       <c r="U25">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
         <v>3.6</v>
@@ -4556,7 +4556,7 @@
         <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="R26">
         <v>2.25</v>
@@ -4571,7 +4571,7 @@
         <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.11</v>
@@ -4583,16 +4583,16 @@
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>2.64</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="P30">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q30">
         <v>2.91</v>
@@ -5223,10 +5223,10 @@
         <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5238,7 +5238,7 @@
         <v>4.95</v>
       </c>
       <c r="AA30">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
         <v>2.35</v>
@@ -5253,10 +5253,10 @@
         <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P31">
         <v>6.5</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="O32">
         <v>3.5</v>
@@ -5537,7 +5537,7 @@
         <v>2.28</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S32">
         <v>1.3</v>
@@ -5546,7 +5546,7 @@
         <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
         <v>1.44</v>
@@ -5598,7 +5598,7 @@
         <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5703,7 +5703,7 @@
         <v>2.6</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
         <v>3.5</v>
@@ -5718,7 +5718,7 @@
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
         <v>1.17</v>
@@ -5745,7 +5745,7 @@
         <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.04</v>
       </c>
       <c r="AK33">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="P35">
-        <v>5.56</v>
+        <v>5.8</v>
       </c>
       <c r="Q35">
         <v>1.95</v>
@@ -6029,13 +6029,13 @@
         <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6071,7 +6071,7 @@
         <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK35">
         <v>2.38</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O36">
         <v>4</v>
       </c>
       <c r="P36">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q36">
         <v>5.05</v>
@@ -6219,7 +6219,7 @@
         <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
         <v>2.45</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O38">
         <v>3.6</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="Q39">
         <v>3.3</v>
@@ -6693,7 +6693,7 @@
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O40">
         <v>3.1</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
         <v>3.7</v>
@@ -7019,7 +7019,7 @@
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O42">
         <v>3</v>
       </c>
       <c r="P42">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -7185,13 +7185,13 @@
         <v>1.03</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z42">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AA42">
         <v>2.15</v>
@@ -7200,13 +7200,13 @@
         <v>1.6</v>
       </c>
       <c r="AC42">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AD42">
         <v>1.18</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
         <v>1.85</v>
@@ -7327,19 +7327,19 @@
         <v>2.97</v>
       </c>
       <c r="Q43">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U43">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
         <v>1.65</v>
@@ -7372,10 +7372,10 @@
         <v>1.28</v>
       </c>
       <c r="AF43">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7810,31 +7810,31 @@
         <v>2.7</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S46">
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V46">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.03</v>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>2.35</v>
       </c>
       <c r="O47">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="P47">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="Q47">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S47">
         <v>1.45</v>
@@ -8012,7 +8012,7 @@
         <v>2.1</v>
       </c>
       <c r="AB47">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC47">
         <v>4.1</v>
@@ -8027,7 +8027,7 @@
         <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
         <v>1.56</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
         <v>2.07</v>
       </c>
       <c r="Q48">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
         <v>2.24</v>
@@ -8187,7 +8187,7 @@
         <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG48">
         <v>2.32</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
         <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>2.84</v>
       </c>
       <c r="R49">
         <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U49">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
         <v>1.08</v>
@@ -8335,7 +8335,7 @@
         <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB49">
         <v>1.98</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -8474,19 +8474,19 @@
         <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U50">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
         <v>1.67</v>
       </c>
       <c r="W50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>1.02</v>
@@ -8803,7 +8803,7 @@
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U52">
         <v>3</v>
@@ -8951,13 +8951,13 @@
         <v>2.7</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
         <v>2.54</v>
       </c>
       <c r="Q53">
-        <v>3.43</v>
+        <v>3.07</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8966,7 +8966,7 @@
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U53">
         <v>2.88</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>4.33</v>
       </c>
       <c r="Q55">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R55">
         <v>2.11</v>
@@ -9313,10 +9313,10 @@
         <v>3.25</v>
       </c>
       <c r="AA55">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB55">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC55">
         <v>3.5</v>
@@ -9328,7 +9328,7 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG55">
         <v>1.83</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AK55">
         <v>1.91</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="O56">
         <v>3.9</v>
       </c>
       <c r="P56">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9452,10 +9452,10 @@
         <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
-        <v>3.24</v>
+        <v>2.87</v>
       </c>
       <c r="U56">
         <v>2.46</v>
@@ -9488,7 +9488,7 @@
         <v>1.35</v>
       </c>
       <c r="AE56">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF56">
         <v>1.85</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O57">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="P57">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9621,7 +9621,7 @@
         <v>2.2</v>
       </c>
       <c r="U57">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="V57">
         <v>1.19</v>
@@ -9639,7 +9639,7 @@
         <v>2.1</v>
       </c>
       <c r="AA57">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB57">
         <v>1.36</v>
@@ -9654,10 +9654,10 @@
         <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG57">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>3.5</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -10113,7 +10113,7 @@
         <v>2.5</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
         <v>1.11</v>
@@ -10131,7 +10131,7 @@
         <v>1.67</v>
       </c>
       <c r="AB60">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC60">
         <v>2.75</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK60">
         <v>1.8</v>
@@ -10261,25 +10261,25 @@
         <v>19</v>
       </c>
       <c r="Q61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R61">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="S61">
         <v>1.11</v>
       </c>
       <c r="T61">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U61">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="V61">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="W61">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -10291,25 +10291,25 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AA61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB61">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AC61">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AD61">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AE61">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF61">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG61">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.02</v>
       </c>
       <c r="AK61">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O62">
         <v>2.7</v>
@@ -10457,7 +10457,7 @@
         <v>3.4</v>
       </c>
       <c r="AB62">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC62">
         <v>6.45</v>
@@ -10943,7 +10943,7 @@
         <v>3.5</v>
       </c>
       <c r="AA65">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB65">
         <v>1.88</v>
@@ -11254,7 +11254,7 @@
         <v>2.36</v>
       </c>
       <c r="V67">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
         <v>1.08</v>
@@ -11284,7 +11284,7 @@
         <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG67">
         <v>2.2</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
         <v>1.62</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>1.94</v>
       </c>
       <c r="AB3">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
         <v>3.25</v>
@@ -1018,7 +1018,7 @@
         <v>2.24</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.03</v>
       </c>
       <c r="AK4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
         <v>2.5</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="AK10">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>2.14</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
         <v>4</v>
@@ -2597,7 +2597,7 @@
         <v>3</v>
       </c>
       <c r="P14">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q14">
         <v>3.07</v>
@@ -2615,7 +2615,7 @@
         <v>3.38</v>
       </c>
       <c r="V14">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2630,7 +2630,7 @@
         <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB14">
         <v>1.57</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O15">
         <v>3.7</v>
       </c>
       <c r="P15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q15">
         <v>2.25</v>
@@ -3086,7 +3086,7 @@
         <v>3.5</v>
       </c>
       <c r="P17">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q17">
         <v>3.08</v>
@@ -3744,19 +3744,19 @@
         <v>2.59</v>
       </c>
       <c r="R21">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T21">
         <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3768,19 +3768,19 @@
         <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA21">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="O23">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P23">
-        <v>6.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q23">
         <v>1.81</v>
@@ -4106,7 +4106,7 @@
         <v>2.52</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
         <v>1.13</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
         <v>3.1</v>
@@ -4233,7 +4233,7 @@
         <v>2.95</v>
       </c>
       <c r="R24">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
         <v>1.41</v>
@@ -4260,13 +4260,13 @@
         <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
         <v>1.65</v>
       </c>
       <c r="AC24">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4414,7 +4414,7 @@
         <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
@@ -4426,7 +4426,7 @@
         <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AC25">
         <v>2.43</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O26">
         <v>3.6</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q26">
         <v>4.15</v>
@@ -4586,13 +4586,13 @@
         <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
         <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
@@ -5045,7 +5045,7 @@
         <v>3.33</v>
       </c>
       <c r="Q29">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="R29">
         <v>2.1</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="O30">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>2.3</v>
@@ -5214,7 +5214,7 @@
         <v>2.27</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
         <v>3.7</v>
@@ -5238,16 +5238,16 @@
         <v>4.95</v>
       </c>
       <c r="AA30">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB30">
         <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD30">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE30">
         <v>1.18</v>
@@ -5371,16 +5371,16 @@
         <v>6.5</v>
       </c>
       <c r="Q31">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R31">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S31">
         <v>1.2</v>
       </c>
       <c r="T31">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U31">
         <v>2</v>
@@ -5392,13 +5392,13 @@
         <v>1.18</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5407,13 +5407,13 @@
         <v>2.75</v>
       </c>
       <c r="AC31">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AD31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE31">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF31">
         <v>1.55</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="O32">
+        <v>4.6</v>
+      </c>
+      <c r="P32">
+        <v>7</v>
+      </c>
+      <c r="Q32">
+        <v>1.78</v>
+      </c>
+      <c r="R32">
+        <v>2.6</v>
+      </c>
+      <c r="S32">
+        <v>1.25</v>
+      </c>
+      <c r="T32">
         <v>3.5</v>
       </c>
-      <c r="P32">
-        <v>4.22</v>
-      </c>
-      <c r="Q32">
-        <v>2.28</v>
-      </c>
-      <c r="R32">
-        <v>2.19</v>
-      </c>
-      <c r="S32">
-        <v>1.3</v>
-      </c>
-      <c r="T32">
-        <v>2.88</v>
-      </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>2.06</v>
+        <v>2.99</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>7</v>
+        <v>4.22</v>
       </c>
       <c r="Q33">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="R33">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="U33">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AC33">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O35">
         <v>3.92</v>
@@ -6050,7 +6050,7 @@
         <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AA35">
         <v>1.9</v>
@@ -6219,7 +6219,7 @@
         <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
         <v>2.45</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>4.85</v>
+        <v>5.31</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O39">
         <v>3.2</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
         <v>3.7</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O42">
         <v>3</v>
@@ -7360,10 +7360,10 @@
         <v>1.43</v>
       </c>
       <c r="AB43">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="AC43">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD43">
         <v>1.64</v>
@@ -7813,7 +7813,7 @@
         <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q46">
         <v>2.97</v>
@@ -7828,7 +7828,7 @@
         <v>3.25</v>
       </c>
       <c r="U46">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
         <v>1.5</v>
@@ -7843,13 +7843,13 @@
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="AA46">
         <v>1.7</v>
       </c>
       <c r="AB46">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC46">
         <v>2.88</v>
@@ -7979,16 +7979,16 @@
         <v>3.1</v>
       </c>
       <c r="Q47">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R47">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
         <v>1.45</v>
       </c>
       <c r="T47">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U47">
         <v>2.88</v>
@@ -8003,25 +8003,25 @@
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z47">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AA47">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB47">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC47">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AD47">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE47">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF47">
         <v>1.85</v>
@@ -8145,7 +8145,7 @@
         <v>3.5</v>
       </c>
       <c r="R48">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S48">
         <v>1.29</v>
@@ -8157,19 +8157,19 @@
         <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z48">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA48">
         <v>1.71</v>
@@ -8178,19 +8178,19 @@
         <v>2.22</v>
       </c>
       <c r="AC48">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AD48">
         <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK48">
         <v>1.33</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O49">
         <v>3.45</v>
@@ -8338,7 +8338,7 @@
         <v>1.71</v>
       </c>
       <c r="AB49">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC49">
         <v>2.88</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
+        <v>3.5</v>
+      </c>
+      <c r="Q50">
+        <v>2.3</v>
+      </c>
+      <c r="R50">
+        <v>2.4</v>
+      </c>
+      <c r="S50">
+        <v>1.25</v>
+      </c>
+      <c r="T50">
         <v>3.6</v>
       </c>
-      <c r="Q50">
-        <v>2.2</v>
-      </c>
-      <c r="R50">
-        <v>2.5</v>
-      </c>
-      <c r="S50">
-        <v>1.22</v>
-      </c>
-      <c r="T50">
-        <v>3.9</v>
-      </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA50">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB50">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AC50">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AG50">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8803,7 +8803,7 @@
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
         <v>3</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AK52">
         <v>1.4</v>
@@ -8951,10 +8951,10 @@
         <v>2.7</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="Q53">
         <v>3.07</v>
@@ -8981,7 +8981,7 @@
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z53">
         <v>3.42</v>
@@ -8990,7 +8990,7 @@
         <v>2.08</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC53">
         <v>3.66</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O55">
         <v>3.3</v>
@@ -9283,7 +9283,7 @@
         <v>4.33</v>
       </c>
       <c r="Q55">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R55">
         <v>2.11</v>
@@ -9298,7 +9298,7 @@
         <v>2.88</v>
       </c>
       <c r="V55">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
         <v>1.06</v>
@@ -9313,7 +9313,7 @@
         <v>3.25</v>
       </c>
       <c r="AA55">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB55">
         <v>1.75</v>
@@ -9331,7 +9331,7 @@
         <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AK55">
         <v>1.91</v>
@@ -9440,7 +9440,7 @@
         <v>1.43</v>
       </c>
       <c r="O56">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P56">
         <v>5.25</v>
@@ -9452,16 +9452,16 @@
         <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U56">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V56">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
         <v>1.11</v>
@@ -9473,7 +9473,7 @@
         <v>1.23</v>
       </c>
       <c r="Z56">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="AA56">
         <v>1.79</v>
@@ -9630,25 +9630,25 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y57">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z57">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AA57">
         <v>3.1</v>
       </c>
       <c r="AB57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC57">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="AD57">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE57">
         <v>1.03</v>
@@ -9784,10 +9784,10 @@
         <v>3.4</v>
       </c>
       <c r="U58">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V58">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W58">
         <v>1.12</v>
@@ -9802,10 +9802,10 @@
         <v>4.4</v>
       </c>
       <c r="AA58">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB58">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
         <v>2.33</v>
@@ -10098,7 +10098,7 @@
         <v>3.33</v>
       </c>
       <c r="Q60">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R60">
         <v>2.25</v>
@@ -10131,7 +10131,7 @@
         <v>1.67</v>
       </c>
       <c r="AB60">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC60">
         <v>2.75</v>
@@ -10433,7 +10433,7 @@
         <v>1.6</v>
       </c>
       <c r="T62">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U62">
         <v>4</v>
@@ -10448,10 +10448,10 @@
         <v>1.1</v>
       </c>
       <c r="Y62">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Z62">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AA62">
         <v>3.4</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P2">
         <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,13 +801,13 @@
         <v>1.98</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R3">
         <v>2.06</v>
@@ -837,7 +837,7 @@
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
         <v>1.85</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
         <v>1.79</v>
@@ -1145,10 +1145,10 @@
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="P6">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AB6">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P7">
+        <v>2.75</v>
+      </c>
+      <c r="Q7">
         <v>3.3</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AB7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="O8">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="P8">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
         <v>3.75</v>
@@ -1628,16 +1628,16 @@
         <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="T8">
         <v>2.3</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
         <v>1.01</v>
@@ -1652,7 +1652,7 @@
         <v>2.29</v>
       </c>
       <c r="AA8">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AB8">
         <v>1.39</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -1797,7 +1797,7 @@
         <v>2.38</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -1812,7 +1812,7 @@
         <v>1.55</v>
       </c>
       <c r="Z9">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AA9">
         <v>2.62</v>
@@ -1821,10 +1821,10 @@
         <v>1.44</v>
       </c>
       <c r="AC9">
-        <v>5.54</v>
+        <v>5.62</v>
       </c>
       <c r="AD9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
@@ -2012,7 +2012,7 @@
         <v>2.1</v>
       </c>
       <c r="AK10">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q11">
         <v>2.94</v>
@@ -2123,7 +2123,7 @@
         <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
         <v>1.35</v>
@@ -2141,19 +2141,19 @@
         <v>2.9</v>
       </c>
       <c r="AA11">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AB11">
         <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
         <v>1.85</v>
@@ -2307,7 +2307,7 @@
         <v>1.47</v>
       </c>
       <c r="AB12">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC12">
         <v>2.15</v>
@@ -2437,28 +2437,28 @@
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="U13">
         <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.17</v>
@@ -2467,25 +2467,25 @@
         <v>4.33</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
         <v>2.62</v>
       </c>
       <c r="AD13">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
         <v>3.7</v>
@@ -2775,10 +2775,10 @@
         <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.1</v>
@@ -2811,7 +2811,7 @@
         <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>2.82</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
         <v>2.2</v>
@@ -3095,19 +3095,19 @@
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
         <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V17">
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3122,7 +3122,7 @@
         <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AC17">
         <v>2.31</v>
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="O21">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q21">
         <v>2.59</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="V21">
         <v>1.6</v>
@@ -3768,28 +3768,28 @@
         <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,7 +4061,7 @@
         <v>1.29</v>
       </c>
       <c r="O23">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>9.550000000000001</v>
@@ -4260,10 +4260,10 @@
         <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB24">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC24">
         <v>4.1</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
         <v>1.95</v>
       </c>
       <c r="Q26">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="R26">
         <v>2.25</v>
@@ -4568,7 +4568,7 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V26">
         <v>1.44</v>
@@ -4586,13 +4586,13 @@
         <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB26">
         <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
@@ -4604,7 +4604,7 @@
         <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O27">
         <v>3.74</v>
       </c>
       <c r="P27">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -4725,7 +4725,7 @@
         <v>2.35</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
         <v>3</v>
@@ -4734,10 +4734,10 @@
         <v>2.6</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4752,7 +4752,7 @@
         <v>1.87</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
         <v>3.2</v>
@@ -4767,7 +4767,7 @@
         <v>1.87</v>
       </c>
       <c r="AG27">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>2.15</v>
       </c>
       <c r="O28">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="P28">
         <v>3.7</v>
@@ -4909,7 +4909,7 @@
         <v>1.76</v>
       </c>
       <c r="Z28">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AA28">
         <v>3.4</v>
@@ -5078,7 +5078,7 @@
         <v>2.1</v>
       </c>
       <c r="AB29">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5202,16 +5202,16 @@
         <v>2.75</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P30">
         <v>2.3</v>
       </c>
       <c r="Q30">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="R30">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="S30">
         <v>1.22</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
         <v>1.4</v>
@@ -5365,10 +5365,10 @@
         <v>1.35</v>
       </c>
       <c r="O31">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P31">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q31">
         <v>1.82</v>
@@ -5383,10 +5383,10 @@
         <v>4</v>
       </c>
       <c r="U31">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V31">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W31">
         <v>1.18</v>
@@ -5401,16 +5401,16 @@
         <v>5.2</v>
       </c>
       <c r="AA31">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB31">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AC31">
         <v>2.04</v>
       </c>
       <c r="AD31">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE31">
         <v>1.26</v>
@@ -5552,10 +5552,10 @@
         <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.17</v>
@@ -5691,7 +5691,7 @@
         <v>1.73</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
         <v>4.22</v>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="O34">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P34">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
@@ -5872,7 +5872,7 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
         <v>1.63</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="O36">
         <v>4</v>
@@ -6219,7 +6219,7 @@
         <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AC36">
         <v>2.45</v>
@@ -6234,7 +6234,7 @@
         <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
         <v>3.2</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P42">
         <v>2.91</v>
@@ -7173,7 +7173,7 @@
         <v>1.44</v>
       </c>
       <c r="T42">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U42">
         <v>3.3</v>
@@ -7330,7 +7330,7 @@
         <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S43">
         <v>1.25</v>
@@ -7363,7 +7363,7 @@
         <v>2.66</v>
       </c>
       <c r="AC43">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD43">
         <v>1.64</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7502,7 +7502,7 @@
         <v>2.61</v>
       </c>
       <c r="U44">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="V44">
         <v>1.38</v>
@@ -7511,7 +7511,7 @@
         <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.28</v>
@@ -7520,10 +7520,10 @@
         <v>3.25</v>
       </c>
       <c r="AA44">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB44">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC44">
         <v>3.28</v>
@@ -7535,10 +7535,10 @@
         <v>1.05</v>
       </c>
       <c r="AF44">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
         <v>2.9</v>
       </c>
       <c r="Q45">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="R45">
         <v>2.03</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T45">
         <v>2.73</v>
@@ -7671,7 +7671,7 @@
         <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7686,7 +7686,7 @@
         <v>1.96</v>
       </c>
       <c r="AB45">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
         <v>3.6</v>
@@ -7701,7 +7701,7 @@
         <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7846,10 +7846,10 @@
         <v>4.29</v>
       </c>
       <c r="AA46">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB46">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AC46">
         <v>2.88</v>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T47">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
         <v>2.88</v>
@@ -8006,7 +8006,7 @@
         <v>1.35</v>
       </c>
       <c r="Z47">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="AA47">
         <v>2.13</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O48">
         <v>3.5</v>
@@ -8157,7 +8157,7 @@
         <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W48">
         <v>1.1</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="O52">
         <v>3.2</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O53">
         <v>3.25</v>
@@ -8975,7 +8975,7 @@
         <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
         <v>1.04</v>
@@ -8999,7 +8999,7 @@
         <v>1.28</v>
       </c>
       <c r="AE53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
         <v>1.75</v>
@@ -9292,13 +9292,13 @@
         <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U55">
         <v>2.88</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W55">
         <v>1.06</v>
@@ -9606,7 +9606,7 @@
         <v>2.72</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9784,16 +9784,16 @@
         <v>3.4</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.14</v>
@@ -9808,10 +9808,10 @@
         <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD58">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE58">
         <v>1.17</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O62">
         <v>2.7</v>
@@ -10424,7 +10424,7 @@
         <v>2.65</v>
       </c>
       <c r="Q62">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="R62">
         <v>1.8</v>
@@ -10433,7 +10433,7 @@
         <v>1.6</v>
       </c>
       <c r="T62">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U62">
         <v>4</v>
@@ -10445,13 +10445,13 @@
         <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y62">
         <v>1.66</v>
       </c>
       <c r="Z62">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AA62">
         <v>3.4</v>
@@ -10460,16 +10460,16 @@
         <v>1.33</v>
       </c>
       <c r="AC62">
-        <v>6.45</v>
+        <v>7.5</v>
       </c>
       <c r="AD62">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE62">
         <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG62">
         <v>1.5</v>
@@ -10488,7 +10488,7 @@
         <v>1.44</v>
       </c>
       <c r="AK62">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>2.26</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA64">
         <v>2.05</v>
       </c>
       <c r="AB64">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q4">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.21</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q6">
-        <v>5.73</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S6">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="T6">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="U6">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
         <v>1.03</v>
@@ -1320,31 +1320,31 @@
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AA6">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="AB6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AC6">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="AD6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.52</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="P7">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
-        <v>3.3</v>
+        <v>5.73</v>
       </c>
       <c r="R7">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S7">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="T7">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="U7">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="V7">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
         <v>1.03</v>
@@ -1483,31 +1483,31 @@
         <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z7">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AA7">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AB7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC7">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="AD7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AG7">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>2.23</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
         <v>4.1</v>
@@ -2286,7 +2286,7 @@
         <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V12">
         <v>1.67</v>
@@ -2597,7 +2597,7 @@
         <v>3</v>
       </c>
       <c r="P14">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="Q14">
         <v>3.07</v>
@@ -2612,7 +2612,7 @@
         <v>2.5</v>
       </c>
       <c r="U14">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="V14">
         <v>1.33</v>
@@ -2630,7 +2630,7 @@
         <v>2.56</v>
       </c>
       <c r="AA14">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AB14">
         <v>1.57</v>
@@ -2639,7 +2639,7 @@
         <v>4.75</v>
       </c>
       <c r="AD14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE14">
         <v>1.03</v>
@@ -2763,7 +2763,7 @@
         <v>3.8</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.3</v>
@@ -2971,7 +2971,7 @@
         <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
         <v>2</v>
@@ -3113,19 +3113,19 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>5.06</v>
+        <v>5.1</v>
       </c>
       <c r="AA17">
         <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AC17">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AD17">
         <v>1.6</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
         <v>1.44</v>
@@ -3258,19 +3258,19 @@
         <v>2.31</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>4.4</v>
       </c>
       <c r="P20">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Q20">
         <v>5.5</v>
@@ -3599,7 +3599,7 @@
         <v>1.15</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.12</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q21">
         <v>2.59</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,7 +3753,7 @@
         <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="V21">
         <v>1.6</v>
@@ -3768,19 +3768,19 @@
         <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE21">
         <v>1.18</v>
@@ -3928,31 +3928,31 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q23">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R23">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
         <v>1.29</v>
@@ -4079,22 +4079,22 @@
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA23">
         <v>1.66</v>
@@ -4103,19 +4103,19 @@
         <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
         <v>3.1</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q24">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R24">
         <v>2.05</v>
@@ -4245,7 +4245,7 @@
         <v>3</v>
       </c>
       <c r="V24">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W24">
         <v>1.05</v>
@@ -4260,13 +4260,13 @@
         <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4556,7 +4556,7 @@
         <v>1.95</v>
       </c>
       <c r="Q26">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="R26">
         <v>2.25</v>
@@ -4604,7 +4604,7 @@
         <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
         <v>2.5</v>
@@ -5854,7 +5854,7 @@
         <v>1.45</v>
       </c>
       <c r="O34">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
         <v>4.88</v>
@@ -6186,10 +6186,10 @@
         <v>1.6</v>
       </c>
       <c r="Q36">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="R36">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6204,7 +6204,7 @@
         <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6506,7 +6506,7 @@
         <v>1.57</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P38">
         <v>5.31</v>
@@ -7158,10 +7158,10 @@
         <v>2.4</v>
       </c>
       <c r="O42">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -7173,7 +7173,7 @@
         <v>1.44</v>
       </c>
       <c r="T42">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U42">
         <v>3.3</v>
@@ -7194,25 +7194,25 @@
         <v>2.75</v>
       </c>
       <c r="AA42">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AB42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC42">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AD42">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE42">
         <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -8172,10 +8172,10 @@
         <v>4.25</v>
       </c>
       <c r="AA48">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB48">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AC48">
         <v>2.62</v>
@@ -8338,7 +8338,7 @@
         <v>1.71</v>
       </c>
       <c r="AB49">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AC49">
         <v>2.88</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -8474,40 +8474,40 @@
         <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="V50">
         <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA50">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB50">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AC50">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD50">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
         <v>1.2</v>
@@ -8664,7 +8664,7 @@
         <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
         <v>2.78</v>
@@ -8954,10 +8954,10 @@
         <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="Q53">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8990,13 +8990,13 @@
         <v>2.08</v>
       </c>
       <c r="AB53">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC53">
         <v>3.66</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
         <v>1.44</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R54">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S54">
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="U54">
         <v>2.9</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
         <v>1.78</v>
@@ -9292,7 +9292,7 @@
         <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U55">
         <v>2.88</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="O56">
         <v>3.95</v>
       </c>
       <c r="P56">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9455,7 +9455,7 @@
         <v>1.34</v>
       </c>
       <c r="T56">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U56">
         <v>2.44</v>
@@ -10098,7 +10098,7 @@
         <v>3.33</v>
       </c>
       <c r="Q60">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R60">
         <v>2.25</v>
@@ -10258,13 +10258,13 @@
         <v>9.5</v>
       </c>
       <c r="P61">
-        <v>19</v>
+        <v>15.55</v>
       </c>
       <c r="Q61">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R61">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="S61">
         <v>1.11</v>
@@ -10273,10 +10273,10 @@
         <v>6</v>
       </c>
       <c r="U61">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="V61">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="W61">
         <v>1.4</v>
@@ -10291,19 +10291,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AA61">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB61">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AC61">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AD61">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AE61">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF61">
         <v>1.91</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="O66">
         <v>4.5</v>
       </c>
       <c r="P66">
-        <v>6.9</v>
+        <v>8.25</v>
       </c>
       <c r="Q66">
         <v>1.79</v>
@@ -11085,7 +11085,7 @@
         <v>1.34</v>
       </c>
       <c r="T66">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U66">
         <v>2.6</v>
@@ -11094,7 +11094,7 @@
         <v>1.44</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11103,7 +11103,7 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AA66">
         <v>1.89</v>
@@ -11112,10 +11112,10 @@
         <v>1.9</v>
       </c>
       <c r="AC66">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE66">
         <v>1.12</v>
@@ -11124,7 +11124,7 @@
         <v>2.26</v>
       </c>
       <c r="AG66">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O68">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q68">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R68">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S68">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T68">
         <v>2.39</v>
       </c>
       <c r="U68">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="V68">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.07</v>
@@ -11429,7 +11429,7 @@
         <v>1.42</v>
       </c>
       <c r="Z68">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AA68">
         <v>2.38</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
         <v>3.1</v>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="Q5">
         <v>1.96</v>
@@ -1166,7 +1166,7 @@
         <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC5">
         <v>2.78</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="O8">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="P8">
         <v>2.5</v>
@@ -1658,10 +1658,10 @@
         <v>1.39</v>
       </c>
       <c r="AC8">
-        <v>5.57</v>
+        <v>5.72</v>
       </c>
       <c r="AD8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1812,7 +1812,7 @@
         <v>1.55</v>
       </c>
       <c r="Z9">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA9">
         <v>2.62</v>
@@ -1821,7 +1821,7 @@
         <v>1.44</v>
       </c>
       <c r="AC9">
-        <v>5.62</v>
+        <v>5.68</v>
       </c>
       <c r="AD9">
         <v>1.14</v>
@@ -1945,7 +1945,7 @@
         <v>3.75</v>
       </c>
       <c r="P10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q10">
         <v>4.41</v>
@@ -1957,7 +1957,7 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U10">
         <v>2.5</v>
@@ -1969,13 +1969,13 @@
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA10">
         <v>1.79</v>
@@ -1984,10 +1984,10 @@
         <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="AD10">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -2277,7 +2277,7 @@
         <v>1.57</v>
       </c>
       <c r="R12">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S12">
         <v>1.22</v>
@@ -2286,13 +2286,13 @@
         <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
         <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2594,7 +2594,7 @@
         <v>2.5</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P14">
         <v>2.57</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q15">
         <v>2.3</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2938,7 +2938,7 @@
         <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2947,13 +2947,13 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
         <v>1.95</v>
@@ -2968,13 +2968,13 @@
         <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
         <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="O17">
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q17">
         <v>3.08</v>
@@ -3113,25 +3113,25 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>5.1</v>
+        <v>5.16</v>
       </c>
       <c r="AA17">
         <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AC17">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
         <v>1.44</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q18">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3264,43 +3264,43 @@
         <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
         <v>4.8</v>
       </c>
       <c r="AA18">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD18">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE18">
         <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3427,43 +3427,43 @@
         <v>3.6</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
         <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB19">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC19">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AD19">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE19">
         <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>2.4</v>
       </c>
       <c r="Q21">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="R21">
         <v>2.32</v>
@@ -3753,7 +3753,7 @@
         <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
         <v>1.6</v>
@@ -3780,7 +3780,7 @@
         <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE21">
         <v>1.18</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R22">
         <v>2</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T22">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U22">
         <v>2.9</v>
@@ -3928,31 +3928,31 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z22">
         <v>3</v>
       </c>
       <c r="AA22">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>9.550000000000001</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>1.83</v>
@@ -4097,13 +4097,13 @@
         <v>4</v>
       </c>
       <c r="AA23">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB23">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AD23">
         <v>1.4</v>
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="Q24">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="R24">
         <v>2.05</v>
@@ -4263,10 +4263,10 @@
         <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC24">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4390,10 +4390,10 @@
         <v>4</v>
       </c>
       <c r="P25">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="Q25">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="R25">
         <v>2.4</v>
@@ -4414,28 +4414,28 @@
         <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
         <v>4.7</v>
       </c>
       <c r="AA25">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
         <v>2.37</v>
       </c>
       <c r="AC25">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AD25">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
         <v>1.62</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>3.5</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
         <v>1.95</v>
@@ -4568,7 +4568,7 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="V26">
         <v>1.44</v>
@@ -4577,13 +4577,13 @@
         <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
         <v>1.73</v>
@@ -4592,7 +4592,7 @@
         <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
+        <v>1.21</v>
+      </c>
+      <c r="AK26">
         <v>1.22</v>
-      </c>
-      <c r="AK26">
-        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5075,13 +5075,13 @@
         <v>2.92</v>
       </c>
       <c r="AA29">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD29">
         <v>1.22</v>
@@ -5365,10 +5365,10 @@
         <v>1.35</v>
       </c>
       <c r="O31">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P31">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="Q31">
         <v>1.82</v>
@@ -5546,7 +5546,7 @@
         <v>3.5</v>
       </c>
       <c r="U32">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V32">
         <v>1.57</v>
@@ -5691,7 +5691,7 @@
         <v>1.73</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
         <v>4.22</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="O36">
         <v>4</v>
@@ -6186,10 +6186,10 @@
         <v>1.6</v>
       </c>
       <c r="Q36">
-        <v>5.07</v>
+        <v>5.16</v>
       </c>
       <c r="R36">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="O38">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P38">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q41">
         <v>2.45</v>
@@ -7034,7 +7034,7 @@
         <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
         <v>3.1</v>
@@ -7197,7 +7197,7 @@
         <v>2.24</v>
       </c>
       <c r="AB42">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC42">
         <v>4.15</v>
@@ -7348,28 +7348,28 @@
         <v>1.14</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
         <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA43">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AC43">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AD43">
         <v>1.64</v>
       </c>
       <c r="AE43">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
         <v>1.72</v>
@@ -7843,10 +7843,10 @@
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB46">
         <v>2.14</v>
@@ -8009,7 +8009,7 @@
         <v>3.25</v>
       </c>
       <c r="AA47">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB47">
         <v>1.74</v>
@@ -8302,7 +8302,7 @@
         <v>3.45</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
         <v>2.84</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
+        <v>3.7</v>
+      </c>
+      <c r="P50">
         <v>3.6</v>
-      </c>
-      <c r="P50">
-        <v>3.4</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -8480,13 +8480,13 @@
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8495,28 +8495,28 @@
         <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA50">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB50">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AC50">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AD50">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8788,7 +8788,7 @@
         <v>2.69</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P52">
         <v>2.45</v>
@@ -8806,7 +8806,7 @@
         <v>2.7</v>
       </c>
       <c r="U52">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V52">
         <v>1.33</v>
@@ -8827,13 +8827,13 @@
         <v>2.16</v>
       </c>
       <c r="AB52">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC52">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="AD52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE52">
         <v>1.04</v>
@@ -8954,10 +8954,10 @@
         <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="Q53">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R53">
         <v>2.2</v>
@@ -8990,13 +8990,13 @@
         <v>2.08</v>
       </c>
       <c r="AB53">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC53">
         <v>3.66</v>
       </c>
       <c r="AD53">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
@@ -9005,7 +9005,7 @@
         <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
         <v>1.44</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O54">
         <v>3.55</v>
       </c>
       <c r="P54">
-        <v>4</v>
+        <v>3.53</v>
       </c>
       <c r="Q54">
         <v>2.32</v>
@@ -9129,7 +9129,7 @@
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U54">
         <v>2.9</v>
@@ -9144,10 +9144,10 @@
         <v>1.05</v>
       </c>
       <c r="Y54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA54">
         <v>2.05</v>
@@ -9159,7 +9159,7 @@
         <v>3.5</v>
       </c>
       <c r="AD54">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE54">
         <v>1.07</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
         <v>1.78</v>
@@ -9280,10 +9280,10 @@
         <v>3.3</v>
       </c>
       <c r="P55">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q55">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R55">
         <v>2.11</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O56">
         <v>3.95</v>
@@ -9476,19 +9476,19 @@
         <v>3.97</v>
       </c>
       <c r="AA56">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB56">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC56">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD56">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF56">
         <v>1.85</v>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O57">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="P57">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9642,7 +9642,7 @@
         <v>3.1</v>
       </c>
       <c r="AB57">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC57">
         <v>7</v>
@@ -9793,7 +9793,7 @@
         <v>1.15</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.14</v>
@@ -9935,22 +9935,22 @@
         <v>1.64</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -9965,25 +9965,25 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
         <v>0</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O60">
         <v>3.5</v>
@@ -10098,10 +10098,10 @@
         <v>3.33</v>
       </c>
       <c r="Q60">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R60">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S60">
         <v>1.29</v>
@@ -10128,13 +10128,13 @@
         <v>4.1</v>
       </c>
       <c r="AA60">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB60">
         <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD60">
         <v>1.4</v>
@@ -10146,7 +10146,7 @@
         <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
         <v>1.8</v>
@@ -10255,10 +10255,10 @@
         <v>1.07</v>
       </c>
       <c r="O61">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="P61">
-        <v>15.55</v>
+        <v>19</v>
       </c>
       <c r="Q61">
         <v>1.33</v>
@@ -10469,7 +10469,7 @@
         <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG62">
         <v>1.5</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11106,7 +11106,7 @@
         <v>3.63</v>
       </c>
       <c r="AA66">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB66">
         <v>1.9</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AK66">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG68">
         <v>1.75</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="Q15">
         <v>2.3</v>
@@ -2796,7 +2796,7 @@
         <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AC15">
         <v>2.63</v>
@@ -2811,7 +2811,7 @@
         <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3264,43 +3264,43 @@
         <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
         <v>4.8</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC18">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE18">
         <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3427,43 +3427,43 @@
         <v>3.6</v>
       </c>
       <c r="U19">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
         <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB19">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC19">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD19">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
         <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4384,37 +4384,37 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P25">
-        <v>6.3</v>
+        <v>5.55</v>
       </c>
       <c r="Q25">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
         <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.14</v>
@@ -4426,7 +4426,7 @@
         <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="AC25">
         <v>2.31</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W30">
         <v>1.17</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P34">
         <v>4.88</v>
@@ -5899,7 +5899,7 @@
         <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE34">
         <v>1.2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O35">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R35">
         <v>2.25</v>
@@ -6050,7 +6050,7 @@
         <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
         <v>1.9</v>
@@ -6059,7 +6059,7 @@
         <v>1.9</v>
       </c>
       <c r="AC35">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
         <v>1.28</v>
@@ -6068,7 +6068,7 @@
         <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG35">
         <v>1.83</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,46 +6340,46 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="O37">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q37">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="R37">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
         <v>1.35</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB37">
         <v>1.85</v>
@@ -6391,13 +6391,13 @@
         <v>1.27</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
         <v>1.3</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q39">
         <v>3.3</v>
@@ -6705,10 +6705,10 @@
         <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB39">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -6835,7 +6835,7 @@
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
         <v>2.91</v>
@@ -6853,7 +6853,7 @@
         <v>2.88</v>
       </c>
       <c r="V40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.06</v>
@@ -6868,7 +6868,7 @@
         <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB40">
         <v>1.8</v>
@@ -6880,7 +6880,7 @@
         <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
         <v>1.73</v>
@@ -8142,13 +8142,13 @@
         <v>2.11</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R48">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
         <v>3.4</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
         <v>1.33</v>
@@ -10750,55 +10750,55 @@
         <v>2.26</v>
       </c>
       <c r="Q64">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="R64">
         <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
         <v>2.61</v>
       </c>
       <c r="U64">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="V64">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W64">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AA64">
         <v>2.05</v>
       </c>
       <c r="AB64">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC64">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AD64">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE64">
         <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AL64">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="R2">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="S2">
         <v>1.17</v>
@@ -656,13 +656,13 @@
         <v>4.5</v>
       </c>
       <c r="U2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V2">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="W2">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -680,7 +680,7 @@
         <v>3.4</v>
       </c>
       <c r="AC2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD2">
         <v>1.93</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC3">
         <v>3.25</v>
@@ -970,55 +970,55 @@
         <v>1.12</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>2.78</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="O6">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P6">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
         <v>3.3</v>
@@ -1456,7 +1456,7 @@
         <v>2.68</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
         <v>5.73</v>
@@ -1468,7 +1468,7 @@
         <v>1.56</v>
       </c>
       <c r="T7">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
         <v>3.35</v>
@@ -1492,7 +1492,7 @@
         <v>2.52</v>
       </c>
       <c r="AB7">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AC7">
         <v>5.15</v>
@@ -1504,7 +1504,7 @@
         <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG7">
         <v>1.57</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P8">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q8">
         <v>3.75</v>
@@ -1640,7 +1640,7 @@
         <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1.08</v>
@@ -1664,7 +1664,7 @@
         <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
         <v>2.2</v>
@@ -1779,10 +1779,10 @@
         <v>2.1</v>
       </c>
       <c r="O9">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -1812,7 +1812,7 @@
         <v>1.55</v>
       </c>
       <c r="Z9">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AA9">
         <v>2.62</v>
@@ -1821,7 +1821,7 @@
         <v>1.44</v>
       </c>
       <c r="AC9">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="AD9">
         <v>1.14</v>
@@ -1849,7 +1849,7 @@
         <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
         <v>1.97</v>
@@ -2012,7 +2012,7 @@
         <v>2.1</v>
       </c>
       <c r="AK10">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P12">
         <v>12.6</v>
@@ -2594,7 +2594,7 @@
         <v>2.5</v>
       </c>
       <c r="O14">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
         <v>2.57</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O16">
         <v>3.2</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
         <v>2.05</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
+        <v>2.5</v>
+      </c>
+      <c r="O19">
+        <v>3.45</v>
+      </c>
+      <c r="P19">
         <v>2.37</v>
-      </c>
-      <c r="O19">
-        <v>3.4</v>
-      </c>
-      <c r="P19">
-        <v>2.45</v>
       </c>
       <c r="Q19">
         <v>2.88</v>
@@ -3451,19 +3451,19 @@
         <v>2.35</v>
       </c>
       <c r="AC19">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE19">
         <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="O20">
         <v>4.4</v>
       </c>
       <c r="P20">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q20">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
         <v>1.22</v>
@@ -3608,7 +3608,7 @@
         <v>4.65</v>
       </c>
       <c r="AA20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB20">
         <v>2.37</v>
@@ -3623,7 +3623,7 @@
         <v>1.21</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
         <v>2.15</v>
@@ -3642,7 +3642,7 @@
         <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q21">
         <v>2.61</v>
@@ -3783,7 +3783,7 @@
         <v>1.59</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
@@ -3949,7 +3949,7 @@
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
         <v>1.87</v>
@@ -4242,7 +4242,7 @@
         <v>2.64</v>
       </c>
       <c r="U24">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
         <v>1.34</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
         <v>3.6</v>
       </c>
       <c r="P26">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q26">
         <v>3.8</v>
@@ -4592,7 +4592,7 @@
         <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
@@ -4719,10 +4719,10 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R27">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="S27">
         <v>1.35</v>
@@ -4752,10 +4752,10 @@
         <v>1.87</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD27">
         <v>1.29</v>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,16 +4879,16 @@
         <v>2.73</v>
       </c>
       <c r="P28">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q28">
         <v>3</v>
       </c>
       <c r="R28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S28">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="T28">
         <v>2.1</v>
@@ -4903,16 +4903,16 @@
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Y28">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Z28">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AA28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AB28">
         <v>1.33</v>
@@ -4927,7 +4927,7 @@
         <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AG28">
         <v>1.47</v>
@@ -5211,22 +5211,22 @@
         <v>2.94</v>
       </c>
       <c r="R30">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
         <v>1.22</v>
       </c>
       <c r="T30">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5244,7 +5244,7 @@
         <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD30">
         <v>1.54</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O32">
         <v>4.6</v>
@@ -5598,7 +5598,7 @@
         <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,7 +5697,7 @@
         <v>4.22</v>
       </c>
       <c r="Q33">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="R33">
         <v>2.19</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="P35">
         <v>6.25</v>
       </c>
       <c r="Q35">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6056,10 +6056,10 @@
         <v>1.9</v>
       </c>
       <c r="AB35">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC35">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD35">
         <v>1.28</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O36">
         <v>4</v>
@@ -6216,7 +6216,7 @@
         <v>4.7</v>
       </c>
       <c r="AA36">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB36">
         <v>2.23</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="O37">
         <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -6355,22 +6355,22 @@
         <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="U37">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.25</v>
@@ -6379,16 +6379,16 @@
         <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AB37">
         <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AD37">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE37">
         <v>1.08</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O38">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>5.06</v>
+        <v>5.01</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
         <v>3.1</v>
       </c>
       <c r="P39">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q39">
         <v>3.3</v>
@@ -6705,7 +6705,7 @@
         <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB39">
         <v>1.7</v>
@@ -6835,7 +6835,7 @@
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q40">
         <v>2.91</v>
@@ -6868,7 +6868,7 @@
         <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
         <v>1.8</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
         <v>1.4</v>
@@ -6998,7 +6998,7 @@
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q41">
         <v>2.45</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
@@ -7327,19 +7327,19 @@
         <v>2.97</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R43">
         <v>2.32</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V43">
         <v>1.65</v>
@@ -7363,7 +7363,7 @@
         <v>2.63</v>
       </c>
       <c r="AC43">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
         <v>1.64</v>
@@ -7490,7 +7490,7 @@
         <v>3.6</v>
       </c>
       <c r="Q44">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
         <v>2.1</v>
@@ -7538,7 +7538,7 @@
         <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,10 +7647,10 @@
         <v>2.2</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P45">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -7668,10 +7668,10 @@
         <v>2.73</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7680,7 +7680,7 @@
         <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA45">
         <v>1.96</v>
@@ -7813,7 +7813,7 @@
         <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q46">
         <v>2.97</v>
@@ -7843,10 +7843,10 @@
         <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="AA46">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB46">
         <v>2.14</v>
@@ -7880,7 +7880,7 @@
         <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8148,7 +8148,7 @@
         <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.4</v>
@@ -8157,7 +8157,7 @@
         <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
         <v>1.1</v>
@@ -8172,10 +8172,10 @@
         <v>4.25</v>
       </c>
       <c r="AA48">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AC48">
         <v>2.62</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O49">
         <v>3.45</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
         <v>2.84</v>
@@ -8498,7 +8498,7 @@
         <v>5.4</v>
       </c>
       <c r="AA50">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB50">
         <v>2.43</v>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51">
@@ -8695,7 +8695,7 @@
         <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8788,7 +8788,7 @@
         <v>2.69</v>
       </c>
       <c r="O52">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
         <v>2.45</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="O53">
         <v>3.25</v>
@@ -8957,10 +8957,10 @@
         <v>2.63</v>
       </c>
       <c r="Q53">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
         <v>1.36</v>
@@ -8978,16 +8978,16 @@
         <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.3</v>
       </c>
       <c r="Z53">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="AA53">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AB53">
         <v>1.78</v>
@@ -9005,7 +9005,7 @@
         <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O54">
         <v>3.55</v>
       </c>
       <c r="P54">
-        <v>3.53</v>
+        <v>3.31</v>
       </c>
       <c r="Q54">
         <v>2.32</v>
@@ -9126,10 +9126,10 @@
         <v>2.01</v>
       </c>
       <c r="S54">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T54">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="U54">
         <v>2.9</v>
@@ -9150,7 +9150,7 @@
         <v>3.4</v>
       </c>
       <c r="AA54">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB54">
         <v>1.75</v>
@@ -9159,16 +9159,16 @@
         <v>3.5</v>
       </c>
       <c r="AD54">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
+        <v>1.83</v>
+      </c>
+      <c r="AG54">
         <v>1.91</v>
-      </c>
-      <c r="AG54">
-        <v>1.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>3.3</v>
       </c>
       <c r="P55">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q55">
         <v>2.39</v>
@@ -9298,19 +9298,19 @@
         <v>2.88</v>
       </c>
       <c r="V55">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
         <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA55">
         <v>2.03</v>
@@ -9328,10 +9328,10 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG55">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O56">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P56">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9458,7 +9458,7 @@
         <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="V56">
         <v>1.5</v>
@@ -9473,7 +9473,7 @@
         <v>1.23</v>
       </c>
       <c r="Z56">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="AA56">
         <v>1.75</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O57">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="P57">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9642,7 +9642,7 @@
         <v>3.1</v>
       </c>
       <c r="AB57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC57">
         <v>7</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="O59">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="Q59">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R59">
-        <v>2.47</v>
+        <v>2.06</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="T59">
-        <v>3.93</v>
+        <v>2.61</v>
       </c>
       <c r="U59">
-        <v>2.11</v>
+        <v>2.89</v>
       </c>
       <c r="V59">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA59">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="AB59">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AC59">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AG59">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
         <v>1.14</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="O60">
         <v>3.5</v>
       </c>
       <c r="P60">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
         <v>2.47</v>
@@ -10131,7 +10131,7 @@
         <v>1.68</v>
       </c>
       <c r="AB60">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC60">
         <v>2.66</v>
@@ -10143,7 +10143,7 @@
         <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
         <v>2.17</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O61">
         <v>9</v>
       </c>
       <c r="P61">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q61">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="R61">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S61">
         <v>1.11</v>
@@ -10273,10 +10273,10 @@
         <v>6</v>
       </c>
       <c r="U61">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V61">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="W61">
         <v>1.4</v>
@@ -10285,31 +10285,31 @@
         <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z61">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA61">
         <v>1.18</v>
       </c>
       <c r="AB61">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AC61">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD61">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AE61">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AF61">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG61">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.02</v>
       </c>
       <c r="AK61">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10469,7 +10469,7 @@
         <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG62">
         <v>1.5</v>
@@ -10578,22 +10578,22 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q63">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="R63">
         <v>3.3</v>
       </c>
       <c r="S63">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T63">
         <v>5.2</v>
@@ -10602,10 +10602,10 @@
         <v>1.85</v>
       </c>
       <c r="V63">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W63">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10614,7 +10614,7 @@
         <v>1.04</v>
       </c>
       <c r="Z63">
-        <v>6.85</v>
+        <v>7.1</v>
       </c>
       <c r="AA63">
         <v>1.3</v>
@@ -10623,19 +10623,19 @@
         <v>3.4</v>
       </c>
       <c r="AC63">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AD63">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AE63">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AF63">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AG63">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK63">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11079,7 +11079,7 @@
         <v>1.79</v>
       </c>
       <c r="R66">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S66">
         <v>1.34</v>
@@ -11088,7 +11088,7 @@
         <v>3</v>
       </c>
       <c r="U66">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V66">
         <v>1.44</v>
@@ -11103,7 +11103,7 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="AA66">
         <v>1.83</v>
@@ -11112,19 +11112,19 @@
         <v>1.9</v>
       </c>
       <c r="AC66">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="AD66">
         <v>1.35</v>
       </c>
       <c r="AE66">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
         <v>2.26</v>
       </c>
       <c r="AG66">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -801,31 +801,31 @@
         <v>2.05</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
         <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
         <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>5.75</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
         <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U5">
         <v>2.44</v>
@@ -1151,7 +1151,7 @@
         <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.03</v>
@@ -1163,19 +1163,19 @@
         <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB5">
         <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
         <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.85</v>
@@ -1948,10 +1948,10 @@
         <v>1.6</v>
       </c>
       <c r="Q10">
-        <v>4.41</v>
+        <v>5.15</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1969,31 +1969,31 @@
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB10">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
         <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2105,43 +2105,43 @@
         <v>2.3</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="R11">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
         <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U11">
         <v>2.88</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB11">
         <v>1.66</v>
@@ -2150,10 +2150,10 @@
         <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
         <v>1.85</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK11">
         <v>1.55</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="O12">
         <v>6.1</v>
@@ -2274,10 +2274,10 @@
         <v>12.6</v>
       </c>
       <c r="Q12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S12">
         <v>1.22</v>
@@ -2286,31 +2286,31 @@
         <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="V12">
         <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
         <v>5.4</v>
       </c>
       <c r="AA12">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB12">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD12">
         <v>1.6</v>
@@ -2319,7 +2319,7 @@
         <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG12">
         <v>1.75</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
+        <v>2.1</v>
+      </c>
+      <c r="O13">
+        <v>3.7</v>
+      </c>
+      <c r="P13">
         <v>2.6</v>
       </c>
-      <c r="O13">
-        <v>3.3</v>
-      </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>2.5</v>
+      </c>
+      <c r="R13">
         <v>2.3</v>
-      </c>
-      <c r="Q13">
-        <v>3.1</v>
-      </c>
-      <c r="R13">
-        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2464,44 +2464,44 @@
         <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC13">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
       </c>
       <c r="AF13">
+        <v>1.56</v>
+      </c>
+      <c r="AG13">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
         <v>1.62</v>
-      </c>
-      <c r="AG13">
-        <v>2.2</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.3</v>
-      </c>
-      <c r="AK13">
-        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P14">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
         <v>3.07</v>
@@ -2606,10 +2606,10 @@
         <v>1.92</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U14">
         <v>3.32</v>
@@ -2618,13 +2618,13 @@
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z14">
         <v>2.56</v>
@@ -2633,7 +2633,7 @@
         <v>2.33</v>
       </c>
       <c r="AB14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
         <v>4.75</v>
@@ -2642,10 +2642,10 @@
         <v>1.15</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG14">
         <v>1.8</v>
@@ -2757,10 +2757,10 @@
         <v>1.76</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
         <v>2.3</v>
@@ -2796,7 +2796,7 @@
         <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
         <v>2.63</v>
@@ -2808,10 +2808,10 @@
         <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P16">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="Q16">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
         <v>2.1</v>
@@ -2950,10 +2950,10 @@
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA16">
         <v>1.95</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
         <v>2.25</v>
@@ -3095,19 +3095,19 @@
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3128,7 +3128,7 @@
         <v>2.31</v>
       </c>
       <c r="AD17">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE17">
         <v>1.25</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q21">
         <v>2.61</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,13 +3753,13 @@
         <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V21">
         <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3780,16 +3780,16 @@
         <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
         <v>3.25</v>
@@ -4100,7 +4100,7 @@
         <v>1.7</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC23">
         <v>2.81</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="Q24">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="R24">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S24">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="U24">
         <v>3.1</v>
@@ -4251,7 +4251,7 @@
         <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.31</v>
@@ -4387,10 +4387,10 @@
         <v>1.53</v>
       </c>
       <c r="O25">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P25">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="Q25">
         <v>1.95</v>
@@ -4423,7 +4423,7 @@
         <v>4.7</v>
       </c>
       <c r="AA25">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB25">
         <v>2.63</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
         <v>1.3</v>
@@ -4583,7 +4583,7 @@
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
         <v>1.73</v>
@@ -4592,7 +4592,7 @@
         <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
         <v>1.4</v>
@@ -5045,7 +5045,7 @@
         <v>3.33</v>
       </c>
       <c r="Q29">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R29">
         <v>2.1</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O30">
         <v>3.66</v>
       </c>
       <c r="P30">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q30">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R30">
         <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U30">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W30">
         <v>1.15</v>
@@ -5235,7 +5235,7 @@
         <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA30">
         <v>1.5</v>
@@ -5244,10 +5244,10 @@
         <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
         <v>1.18</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,10 +5365,10 @@
         <v>1.35</v>
       </c>
       <c r="O31">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="P31">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q31">
         <v>1.82</v>
@@ -5410,7 +5410,7 @@
         <v>2.04</v>
       </c>
       <c r="AD31">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE31">
         <v>1.26</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O32">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="P32">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="Q32">
         <v>1.78</v>
@@ -5543,7 +5543,7 @@
         <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U32">
         <v>2.33</v>
@@ -5573,7 +5573,7 @@
         <v>2.45</v>
       </c>
       <c r="AD32">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE32">
         <v>1.21</v>
@@ -5598,7 +5598,7 @@
         <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,16 +5691,16 @@
         <v>1.73</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
         <v>4.22</v>
       </c>
       <c r="Q33">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="R33">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
         <v>1.3</v>
@@ -5712,7 +5712,7 @@
         <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -6014,55 +6014,55 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="O35">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="V35">
         <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA35">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC35">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
         <v>1.1</v>
@@ -6071,7 +6071,7 @@
         <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.11</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>4.33</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
         <v>1.6</v>
@@ -6213,7 +6213,7 @@
         <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <v>1.61</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -6355,13 +6355,13 @@
         <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
         <v>2.94</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
         <v>1.42</v>
@@ -6373,16 +6373,16 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
         <v>2.92</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>5.01</v>
+        <v>4.1</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O39">
         <v>3.1</v>
@@ -6681,10 +6681,10 @@
         <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
         <v>2.77</v>
@@ -6693,7 +6693,7 @@
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6835,25 +6835,25 @@
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q40">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
         <v>2.88</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
         <v>1.06</v>
@@ -6862,13 +6862,13 @@
         <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB40">
         <v>1.8</v>
@@ -6883,7 +6883,7 @@
         <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
         <v>2</v>
@@ -7065,7 +7065,7 @@
         <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="O42">
         <v>3</v>
       </c>
       <c r="P42">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -7191,7 +7191,7 @@
         <v>1.4</v>
       </c>
       <c r="Z42">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AA42">
         <v>2.24</v>
@@ -7206,13 +7206,13 @@
         <v>1.16</v>
       </c>
       <c r="AE42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
         <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7810,10 +7810,10 @@
         <v>2.7</v>
       </c>
       <c r="O46">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P46">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q46">
         <v>2.97</v>
@@ -7837,10 +7837,10 @@
         <v>1.11</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
         <v>4.36</v>
@@ -7864,7 +7864,7 @@
         <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
         <v>1.38</v>
@@ -7982,13 +7982,13 @@
         <v>2.8</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S47">
         <v>1.49</v>
       </c>
       <c r="T47">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="U47">
         <v>2.88</v>
@@ -8012,7 +8012,7 @@
         <v>2.1</v>
       </c>
       <c r="AB47">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC47">
         <v>3.72</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q49">
         <v>2.84</v>
@@ -8335,10 +8335,10 @@
         <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB49">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
         <v>2.88</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
         <v>3.6</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8480,10 +8480,10 @@
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V50">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
         <v>1.18</v>
@@ -8498,7 +8498,7 @@
         <v>5.4</v>
       </c>
       <c r="AA50">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB50">
         <v>2.43</v>
@@ -8507,7 +8507,7 @@
         <v>2.13</v>
       </c>
       <c r="AD50">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
         <v>1.22</v>
@@ -8532,7 +8532,7 @@
         <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8664,7 +8664,7 @@
         <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC51">
         <v>2.78</v>
@@ -8673,7 +8673,7 @@
         <v>1.34</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
         <v>1.62</v>
@@ -9301,10 +9301,10 @@
         <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.3</v>
@@ -9316,13 +9316,13 @@
         <v>2.03</v>
       </c>
       <c r="AB55">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
         <v>3.5</v>
       </c>
       <c r="AD55">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O56">
         <v>4.1</v>
       </c>
       <c r="P56">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9458,10 +9458,10 @@
         <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W56">
         <v>1.11</v>
@@ -9473,22 +9473,22 @@
         <v>1.23</v>
       </c>
       <c r="Z56">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC56">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD56">
         <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
         <v>1.85</v>
@@ -9510,7 +9510,7 @@
         <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9606,7 +9606,7 @@
         <v>2.79</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9645,7 +9645,7 @@
         <v>1.33</v>
       </c>
       <c r="AC57">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AD57">
         <v>1.07</v>
@@ -9673,7 +9673,7 @@
         <v>1.24</v>
       </c>
       <c r="AK57">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9781,7 +9781,7 @@
         <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U58">
         <v>2.2</v>
@@ -9790,7 +9790,7 @@
         <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9799,28 +9799,28 @@
         <v>1.14</v>
       </c>
       <c r="Z58">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
         <v>1.57</v>
       </c>
       <c r="AB58">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC58">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD58">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
         <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O59">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P59">
         <v>1.91</v>
       </c>
       <c r="Q59">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="R59">
         <v>2.06</v>
@@ -9965,7 +9965,7 @@
         <v>2.97</v>
       </c>
       <c r="AA59">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB59">
         <v>1.69</v>
@@ -9980,10 +9980,10 @@
         <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG59">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P60">
         <v>3.3</v>
@@ -10101,10 +10101,10 @@
         <v>2.47</v>
       </c>
       <c r="R60">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T60">
         <v>3.25</v>
@@ -10125,7 +10125,7 @@
         <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA60">
         <v>1.68</v>
@@ -10137,7 +10137,7 @@
         <v>2.66</v>
       </c>
       <c r="AD60">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE60">
         <v>1.13</v>
@@ -10146,7 +10146,7 @@
         <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10261,49 +10261,49 @@
         <v>16</v>
       </c>
       <c r="Q61">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R61">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="S61">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U61">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V61">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="W61">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z61">
         <v>10</v>
       </c>
       <c r="AA61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB61">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AC61">
+        <v>1.53</v>
+      </c>
+      <c r="AD61">
+        <v>2.25</v>
+      </c>
+      <c r="AE61">
         <v>1.55</v>
-      </c>
-      <c r="AD61">
-        <v>2.24</v>
-      </c>
-      <c r="AE61">
-        <v>1.58</v>
       </c>
       <c r="AF61">
         <v>1.75</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK61">
         <v>5</v>
@@ -10418,19 +10418,19 @@
         <v>2.8</v>
       </c>
       <c r="O62">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P62">
         <v>2.65</v>
       </c>
       <c r="Q62">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R62">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="S62">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="T62">
         <v>2.05</v>
@@ -10454,7 +10454,7 @@
         <v>2.05</v>
       </c>
       <c r="AA62">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB62">
         <v>1.33</v>
@@ -11239,7 +11239,7 @@
         <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
         <v>2.25</v>
@@ -11272,7 +11272,7 @@
         <v>1.67</v>
       </c>
       <c r="AB67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC67">
         <v>2.75</v>
@@ -11284,10 +11284,10 @@
         <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG67">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -810,7 +810,7 @@
         <v>2.3</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.39</v>
@@ -837,10 +837,10 @@
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
         <v>3.25</v>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O5">
         <v>4.2</v>
@@ -1136,7 +1136,7 @@
         <v>1.91</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
         <v>1.3</v>
@@ -1145,37 +1145,37 @@
         <v>3</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA5">
         <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AD5">
         <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>1.85</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="O10">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
         <v>1.6</v>
@@ -1969,7 +1969,7 @@
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
         <v>1.25</v>
@@ -1984,10 +1984,10 @@
         <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
         <v>1.09</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O11">
         <v>3.25</v>
@@ -2114,16 +2114,16 @@
         <v>2.76</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
         <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V11">
         <v>1.33</v>
@@ -2132,28 +2132,28 @@
         <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA11">
         <v>2.17</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD11">
         <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
         <v>1.85</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
         <v>1.55</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O12">
         <v>6.1</v>
       </c>
       <c r="P12">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R12">
         <v>2.8</v>
@@ -2286,7 +2286,7 @@
         <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
         <v>1.67</v>
@@ -2301,25 +2301,25 @@
         <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AC12">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AD12">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE12">
         <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG12">
         <v>1.75</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK12">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2633,10 +2633,10 @@
         <v>2.33</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC14">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AD14">
         <v>1.15</v>
@@ -2757,22 +2757,22 @@
         <v>1.76</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
         <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
         <v>2.4</v>
@@ -2781,7 +2781,7 @@
         <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -2796,7 +2796,7 @@
         <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC15">
         <v>2.63</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
@@ -2938,13 +2938,13 @@
         <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="V16">
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.05</v>
@@ -2959,7 +2959,7 @@
         <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>3.4</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q18">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3264,43 +3264,43 @@
         <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
         <v>4.8</v>
       </c>
       <c r="AA18">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
         <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AG18">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3427,43 +3427,43 @@
         <v>3.6</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
         <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB19">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE19">
         <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="O21">
         <v>3.4</v>
@@ -3753,43 +3753,43 @@
         <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="AD21">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>1.35</v>
       </c>
       <c r="Z22">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA22">
         <v>2.1</v>
@@ -3952,7 +3952,7 @@
         <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q23">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
         <v>1.29</v>
@@ -4079,7 +4079,7 @@
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
         <v>1.5</v>
@@ -4088,28 +4088,28 @@
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
         <v>1.87</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK23">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,19 +4230,19 @@
         <v>3.34</v>
       </c>
       <c r="Q24">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R24">
         <v>1.97</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V24">
         <v>1.34</v>
@@ -4257,19 +4257,19 @@
         <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AA24">
         <v>2.2</v>
       </c>
       <c r="AB24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
         <v>1.04</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>4.55</v>
       </c>
       <c r="P25">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="Q25">
         <v>1.95</v>
@@ -4402,7 +4402,7 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U25">
         <v>2.2</v>
@@ -4423,13 +4423,13 @@
         <v>4.7</v>
       </c>
       <c r="AA25">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AC25">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD25">
         <v>1.68</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -4568,16 +4568,16 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
         <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.22</v>
@@ -4601,7 +4601,7 @@
         <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG26">
         <v>2.14</v>
@@ -5054,13 +5054,13 @@
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
         <v>2.8</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
         <v>1.08</v>
@@ -5069,25 +5069,25 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB29">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC29">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AD29">
         <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O31">
         <v>4.65</v>
@@ -5371,22 +5371,22 @@
         <v>6.5</v>
       </c>
       <c r="Q31">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R31">
         <v>2.51</v>
       </c>
       <c r="S31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
         <v>4</v>
       </c>
       <c r="U31">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V31">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W31">
         <v>1.18</v>
@@ -5398,7 +5398,7 @@
         <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>1.44</v>
@@ -5528,10 +5528,10 @@
         <v>1.33</v>
       </c>
       <c r="O32">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="P32">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>1.78</v>
@@ -5546,13 +5546,13 @@
         <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5564,10 +5564,10 @@
         <v>4.8</v>
       </c>
       <c r="AA32">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB32">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC32">
         <v>2.45</v>
@@ -5576,7 +5576,7 @@
         <v>1.53</v>
       </c>
       <c r="AE32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
         <v>1.85</v>
@@ -5598,7 +5598,7 @@
         <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>4.22</v>
+        <v>4.41</v>
       </c>
       <c r="Q33">
         <v>2.32</v>
@@ -5706,10 +5706,10 @@
         <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
         <v>1.45</v>
@@ -5718,16 +5718,16 @@
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.1</v>
+        <v>4.21</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB33">
         <v>2.08</v>
@@ -5739,7 +5739,7 @@
         <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
         <v>1.67</v>
@@ -5863,22 +5863,22 @@
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S34">
         <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5899,13 +5899,13 @@
         <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
         <v>2.45</v>
@@ -6020,7 +6020,7 @@
         <v>4</v>
       </c>
       <c r="P35">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q35">
         <v>1.94</v>
@@ -6032,10 +6032,10 @@
         <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U35">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
         <v>1.4</v>
@@ -6044,22 +6044,22 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB35">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC35">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
         <v>1.3</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
         <v>1.6</v>
       </c>
       <c r="Q36">
-        <v>5.16</v>
+        <v>5.21</v>
       </c>
       <c r="R36">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6198,7 +6198,7 @@
         <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V36">
         <v>1.62</v>
@@ -6207,7 +6207,7 @@
         <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.12</v>
@@ -6219,10 +6219,10 @@
         <v>1.61</v>
       </c>
       <c r="AB36">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AC36">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD36">
         <v>1.53</v>
@@ -6234,7 +6234,7 @@
         <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>2.05</v>
       </c>
       <c r="Q37">
-        <v>3.6</v>
+        <v>4.12</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S37">
         <v>1.33</v>
@@ -6379,7 +6379,7 @@
         <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
         <v>1.95</v>
@@ -6413,7 +6413,7 @@
         <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>1.65</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P38">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6675,10 +6675,10 @@
         <v>2.4</v>
       </c>
       <c r="Q39">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S39">
         <v>1.36</v>
@@ -6687,7 +6687,7 @@
         <v>2.88</v>
       </c>
       <c r="U39">
-        <v>2.77</v>
+        <v>2.35</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6696,7 +6696,7 @@
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
         <v>1.33</v>
@@ -6708,13 +6708,13 @@
         <v>2.12</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE39">
         <v>1.04</v>
@@ -6723,7 +6723,7 @@
         <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
         <v>1.35</v>
@@ -6865,28 +6865,28 @@
         <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
         <v>1.8</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD40">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE40">
         <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7001,31 +7001,31 @@
         <v>3.7</v>
       </c>
       <c r="Q41">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
         <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z41">
         <v>3.58</v>
@@ -7034,22 +7034,22 @@
         <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
         <v>1.33</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
         <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
         <v>1.87</v>
@@ -7161,55 +7161,55 @@
         <v>3</v>
       </c>
       <c r="P42">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U42">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>2.72</v>
+        <v>3.06</v>
       </c>
       <c r="AA42">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="AB42">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AC42">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AD42">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG42">
         <v>1.87</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7336,16 +7336,16 @@
         <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U43">
         <v>2.15</v>
       </c>
       <c r="V43">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7354,28 +7354,28 @@
         <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA43">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB43">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD43">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>3.45</v>
       </c>
       <c r="P46">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q46">
         <v>2.97</v>
@@ -7840,16 +7840,16 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AB46">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC46">
         <v>2.88</v>
@@ -7864,7 +7864,7 @@
         <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7973,10 +7973,10 @@
         <v>2.35</v>
       </c>
       <c r="O47">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="P47">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q47">
         <v>2.8</v>
@@ -7988,7 +7988,7 @@
         <v>1.49</v>
       </c>
       <c r="T47">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="U47">
         <v>2.88</v>
@@ -8003,13 +8003,13 @@
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z47">
         <v>3.25</v>
       </c>
       <c r="AA47">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB47">
         <v>1.7</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q48">
         <v>3.6</v>
@@ -8151,7 +8151,7 @@
         <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
         <v>2.4</v>
@@ -8166,16 +8166,16 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
         <v>4.25</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB48">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
         <v>2.62</v>
@@ -8184,13 +8184,13 @@
         <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
         <v>1.33</v>
@@ -8299,16 +8299,16 @@
         <v>2.6</v>
       </c>
       <c r="O49">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="P49">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
         <v>2.84</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8317,28 +8317,28 @@
         <v>3.25</v>
       </c>
       <c r="U49">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
         <v>1.7</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AC49">
         <v>2.88</v>
@@ -8347,13 +8347,13 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8486,7 +8486,7 @@
         <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8495,28 +8495,28 @@
         <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA50">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB50">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AC50">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AD50">
         <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8797,13 +8797,13 @@
         <v>3.44</v>
       </c>
       <c r="R52">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S52">
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U52">
         <v>3.24</v>
@@ -8812,10 +8812,10 @@
         <v>1.33</v>
       </c>
       <c r="W52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.36</v>
@@ -8824,25 +8824,25 @@
         <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC52">
-        <v>3.99</v>
+        <v>3.42</v>
       </c>
       <c r="AD52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG52">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.44</v>
       </c>
       <c r="AK52">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="O53">
         <v>3.25</v>
@@ -8957,7 +8957,7 @@
         <v>2.63</v>
       </c>
       <c r="Q53">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="R53">
         <v>2.18</v>
@@ -8969,10 +8969,10 @@
         <v>2.8</v>
       </c>
       <c r="U53">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
         <v>1.05</v>
@@ -9283,28 +9283,28 @@
         <v>4.33</v>
       </c>
       <c r="Q55">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="R55">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="S55">
         <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U55">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V55">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
         <v>1.3</v>
@@ -9322,7 +9322,7 @@
         <v>3.5</v>
       </c>
       <c r="AD55">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
@@ -9331,7 +9331,7 @@
         <v>1.8</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK55">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9443,7 +9443,7 @@
         <v>4.1</v>
       </c>
       <c r="P56">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9458,16 +9458,16 @@
         <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V56">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
         <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
         <v>1.23</v>
@@ -9606,7 +9606,7 @@
         <v>2.79</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9630,13 +9630,13 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y57">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z57">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AA57">
         <v>3.1</v>
@@ -9648,10 +9648,10 @@
         <v>6.1</v>
       </c>
       <c r="AD57">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF57">
         <v>2.3</v>
@@ -9781,7 +9781,7 @@
         <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U58">
         <v>2.2</v>
@@ -9793,7 +9793,7 @@
         <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.14</v>
@@ -9935,7 +9935,7 @@
         <v>1.91</v>
       </c>
       <c r="Q59">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="R59">
         <v>2.06</v>
@@ -9980,7 +9980,7 @@
         <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG59">
         <v>1.79</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O60">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q60">
         <v>2.47</v>
@@ -10116,7 +10116,7 @@
         <v>1.44</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,13 +10125,13 @@
         <v>1.2</v>
       </c>
       <c r="Z60">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA60">
         <v>1.68</v>
       </c>
       <c r="AB60">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC60">
         <v>2.66</v>
@@ -10140,13 +10140,13 @@
         <v>1.44</v>
       </c>
       <c r="AE60">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF60">
         <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK60">
         <v>1.8</v>
@@ -10258,7 +10258,7 @@
         <v>9</v>
       </c>
       <c r="P61">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q61">
         <v>1.4</v>
@@ -10270,7 +10270,7 @@
         <v>1.15</v>
       </c>
       <c r="T61">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U61">
         <v>1.68</v>
@@ -10282,25 +10282,25 @@
         <v>1.3</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z61">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA61">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AB61">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AC61">
         <v>1.53</v>
       </c>
       <c r="AD61">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AE61">
         <v>1.55</v>
@@ -10421,46 +10421,46 @@
         <v>2.65</v>
       </c>
       <c r="P62">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q62">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="R62">
         <v>1.73</v>
       </c>
       <c r="S62">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="T62">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="U62">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W62">
         <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y62">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z62">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AA62">
         <v>3</v>
       </c>
       <c r="AB62">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC62">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
       <c r="AD62">
         <v>1.06</v>
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG62">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.44</v>
       </c>
       <c r="AK62">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10910,7 +10910,7 @@
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q65">
         <v>3.7</v>
@@ -10943,7 +10943,7 @@
         <v>3.5</v>
       </c>
       <c r="AA65">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB65">
         <v>1.88</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
         <v>3.6</v>
       </c>
       <c r="P67">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q67">
         <v>2.7</v>
@@ -11251,7 +11251,7 @@
         <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V67">
         <v>1.44</v>
@@ -11266,22 +11266,22 @@
         <v>1.18</v>
       </c>
       <c r="Z67">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA67">
         <v>1.67</v>
       </c>
       <c r="AB67">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC67">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="AD67">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF67">
         <v>1.57</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -638,7 +638,7 @@
         <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P2">
         <v>2.6</v>
@@ -647,22 +647,22 @@
         <v>2.63</v>
       </c>
       <c r="R2">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="S2">
         <v>1.17</v>
       </c>
       <c r="T2">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="U2">
         <v>1.85</v>
       </c>
       <c r="V2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -677,22 +677,22 @@
         <v>1.33</v>
       </c>
       <c r="AB2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC2">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD2">
         <v>1.93</v>
       </c>
       <c r="AE2">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF2">
         <v>1.3</v>
       </c>
       <c r="AG2">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
         <v>3.07</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P17">
         <v>2.25</v>
@@ -3110,25 +3110,25 @@
         <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
       <c r="AA17">
         <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AC17">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE17">
         <v>1.25</v>
@@ -3137,7 +3137,7 @@
         <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AK17">
         <v>1.44</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC22">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AK22">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O23">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P23">
-        <v>9.550000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="Q23">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S23">
         <v>1.29</v>
@@ -4079,16 +4079,16 @@
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.16</v>
@@ -4097,16 +4097,16 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC23">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
         <v>1.13</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O25">
         <v>4.55</v>
       </c>
       <c r="P25">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="Q25">
         <v>1.95</v>
@@ -4402,10 +4402,10 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V25">
         <v>1.62</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA25">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB25">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC25">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AD25">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE25">
         <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>2.62</v>
       </c>
       <c r="O30">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="P30">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="Q30">
         <v>2.95</v>
@@ -5223,10 +5223,10 @@
         <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5238,7 +5238,7 @@
         <v>5.5</v>
       </c>
       <c r="AA30">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB30">
         <v>2.35</v>
@@ -5250,13 +5250,13 @@
         <v>1.57</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O34">
         <v>4.1</v>
       </c>
       <c r="P34">
-        <v>4.88</v>
+        <v>5.16</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
@@ -5866,7 +5866,7 @@
         <v>2.55</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
         <v>4</v>
@@ -5884,10 +5884,10 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z34">
-        <v>5.2</v>
+        <v>5.35</v>
       </c>
       <c r="AA34">
         <v>1.5</v>
@@ -5896,7 +5896,7 @@
         <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
         <v>1.65</v>
@@ -5908,7 +5908,7 @@
         <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>1.43</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
         <v>6.25</v>
@@ -6044,13 +6044,13 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
         <v>1.82</v>
@@ -6059,13 +6059,13 @@
         <v>1.84</v>
       </c>
       <c r="AC35">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD35">
         <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
         <v>1.95</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK35">
         <v>2.47</v>
@@ -6186,10 +6186,10 @@
         <v>1.6</v>
       </c>
       <c r="Q36">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="R36">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
+        <v>3.2</v>
+      </c>
+      <c r="O37">
+        <v>3.1</v>
+      </c>
+      <c r="P37">
+        <v>2.1</v>
+      </c>
+      <c r="Q37">
+        <v>4.34</v>
+      </c>
+      <c r="R37">
+        <v>2</v>
+      </c>
+      <c r="S37">
+        <v>1.36</v>
+      </c>
+      <c r="T37">
+        <v>2.64</v>
+      </c>
+      <c r="U37">
         <v>3</v>
       </c>
-      <c r="O37">
-        <v>3.25</v>
-      </c>
-      <c r="P37">
-        <v>2.05</v>
-      </c>
-      <c r="Q37">
-        <v>4.12</v>
-      </c>
-      <c r="R37">
-        <v>2.03</v>
-      </c>
-      <c r="S37">
+      <c r="V37">
         <v>1.33</v>
-      </c>
-      <c r="T37">
-        <v>2.94</v>
-      </c>
-      <c r="U37">
-        <v>2.75</v>
-      </c>
-      <c r="V37">
-        <v>1.42</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC37">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AK37">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O47">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="P47">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q47">
         <v>2.8</v>
@@ -7985,16 +7985,16 @@
         <v>2</v>
       </c>
       <c r="S47">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="T47">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="U47">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W47">
         <v>1.07</v>
@@ -8003,10 +8003,10 @@
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z47">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA47">
         <v>2.19</v>
@@ -8021,13 +8021,13 @@
         <v>1.24</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
         <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O48">
         <v>3.6</v>
@@ -8148,13 +8148,13 @@
         <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
         <v>1.51</v>
@@ -8166,16 +8166,16 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z48">
         <v>4.25</v>
       </c>
       <c r="AA48">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC48">
         <v>2.62</v>
@@ -8184,7 +8184,7 @@
         <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
         <v>1.55</v>
@@ -8794,7 +8794,7 @@
         <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>3.44</v>
+        <v>3.64</v>
       </c>
       <c r="R52">
         <v>2</v>
@@ -8806,7 +8806,7 @@
         <v>2.6</v>
       </c>
       <c r="U52">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="V52">
         <v>1.33</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
         <v>2.63</v>
       </c>
       <c r="Q53">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S53">
         <v>1.36</v>
@@ -8969,10 +8969,10 @@
         <v>2.8</v>
       </c>
       <c r="U53">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V53">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W53">
         <v>1.05</v>
@@ -8981,13 +8981,13 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z53">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AA53">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AB53">
         <v>1.78</v>
@@ -8996,7 +8996,7 @@
         <v>3.66</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
@@ -9005,7 +9005,7 @@
         <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9295,10 +9295,10 @@
         <v>2.61</v>
       </c>
       <c r="U55">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
         <v>1.05</v>
@@ -9328,7 +9328,7 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG55">
         <v>1.87</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O64">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P64">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q64">
         <v>3.6</v>
@@ -10756,49 +10756,49 @@
         <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T64">
         <v>2.61</v>
       </c>
       <c r="U64">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V64">
         <v>1.36</v>
       </c>
       <c r="W64">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
         <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="AA64">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB64">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC64">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD64">
         <v>1.21</v>
       </c>
       <c r="AE64">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF64">
         <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AK64">
         <v>1.31</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB69">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC69">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "11"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "22", "31", "36", "54"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,42 +938,42 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="O4">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="P4">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Q4">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R4">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="S4">
         <v>1.23</v>
@@ -982,10 +982,10 @@
         <v>3.7</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
         <v>1.15</v>
@@ -1000,68 +1000,68 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB4">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AD4">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AG4">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "51"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AJ4">
+        <v>1.04</v>
+      </c>
+      <c r="AK4">
         <v>1.02</v>
       </c>
-      <c r="AK4">
-        <v>1.01</v>
-      </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
         <v>1.3</v>
@@ -1148,7 +1148,7 @@
         <v>2.55</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.08</v>
@@ -1160,28 +1160,28 @@
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
         <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC5">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AD5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S6">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="T6">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U6">
         <v>3.5</v>
@@ -1314,7 +1314,7 @@
         <v>1.22</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1.05</v>
@@ -1323,7 +1323,7 @@
         <v>1.47</v>
       </c>
       <c r="Z6">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="AA6">
         <v>2.42</v>
@@ -1341,10 +1341,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG6">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>5.73</v>
+        <v>4.94</v>
       </c>
       <c r="R7">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S7">
         <v>1.56</v>
       </c>
       <c r="T7">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U7">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="V7">
         <v>1.25</v>
@@ -1492,10 +1492,10 @@
         <v>2.52</v>
       </c>
       <c r="AB7">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AC7">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AD7">
         <v>1.1</v>
@@ -1507,7 +1507,7 @@
         <v>2.25</v>
       </c>
       <c r="AG7">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,55 +1613,55 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P8">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="R8">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="S8">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
         <v>2.3</v>
       </c>
       <c r="U8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z8">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AA8">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB8">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC8">
-        <v>5.72</v>
+        <v>6.23</v>
       </c>
       <c r="AD8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
@@ -1670,7 +1670,7 @@
         <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="O9">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="P9">
-        <v>3.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="R9">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="S9">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="T9">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="U9">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
         <v>1.55</v>
       </c>
       <c r="Z9">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="AA9">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB9">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC9">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.4</v>
       </c>
       <c r="AK9">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,42 +1928,42 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q10">
-        <v>5.15</v>
+        <v>4.41</v>
       </c>
       <c r="R10">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.1</v>
@@ -1972,35 +1972,35 @@
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC10">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2012,34 +2012,34 @@
         <v>2.1</v>
       </c>
       <c r="AK10">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2105,16 +2105,16 @@
         <v>2.4</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q11">
         <v>2.76</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
         <v>1.4</v>
@@ -2123,19 +2123,19 @@
         <v>2.7</v>
       </c>
       <c r="U11">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
         <v>2.9</v>
@@ -2147,10 +2147,10 @@
         <v>1.61</v>
       </c>
       <c r="AC11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2271,13 +2271,13 @@
         <v>6.1</v>
       </c>
       <c r="P12">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="Q12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S12">
         <v>1.22</v>
@@ -2307,22 +2307,22 @@
         <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AC12">
         <v>2.24</v>
       </c>
       <c r="AD12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE12">
         <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK12">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="Q13">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="V13">
         <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2464,13 +2464,13 @@
         <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC13">
         <v>2.66</v>
@@ -2482,10 +2482,10 @@
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,52 +2917,52 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="O16">
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U16">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="V16">
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y16">
         <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA16">
         <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD16">
         <v>1.3</v>
@@ -2974,7 +2974,7 @@
         <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
         <v>2.25</v>
       </c>
       <c r="Q17">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="R17">
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
         <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V17">
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
         <v>2.25</v>
@@ -3276,31 +3276,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
       <c r="Q19">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U19">
         <v>2.15</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W19">
         <v>1.17</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA19">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB19">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC19">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AD19">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE19">
         <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -3584,13 +3584,13 @@
         <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T20">
         <v>3.6</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V20">
         <v>1.62</v>
@@ -3602,28 +3602,28 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z20">
         <v>4.65</v>
       </c>
       <c r="AA20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB20">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC20">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AD20">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE20">
         <v>1.21</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
         <v>2.15</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
         <v>2.75</v>
@@ -3744,22 +3744,22 @@
         <v>2.61</v>
       </c>
       <c r="R21">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,28 +3768,28 @@
         <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA21">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="AD21">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG21">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,58 +4221,58 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="R24">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S24">
         <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="V24">
         <v>1.34</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="AA24">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB24">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AD24">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
         <v>1.91</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="V26">
         <v>1.48</v>
@@ -4580,10 +4580,10 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA26">
         <v>1.73</v>
@@ -4601,10 +4601,10 @@
         <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O27">
-        <v>3.74</v>
+        <v>3.88</v>
       </c>
       <c r="P27">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="Q27">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="R27">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA27">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC27">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O28">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="P28">
         <v>3.75</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R28">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S28">
+        <v>1.71</v>
+      </c>
+      <c r="T28">
+        <v>2.05</v>
+      </c>
+      <c r="U28">
+        <v>4.6</v>
+      </c>
+      <c r="V28">
+        <v>1.11</v>
+      </c>
+      <c r="W28">
+        <v>1.02</v>
+      </c>
+      <c r="X28">
+        <v>1.21</v>
+      </c>
+      <c r="Y28">
         <v>1.73</v>
       </c>
-      <c r="T28">
-        <v>2.1</v>
-      </c>
-      <c r="U28">
-        <v>4.2</v>
-      </c>
-      <c r="V28">
-        <v>1.2</v>
-      </c>
-      <c r="W28">
-        <v>1.03</v>
-      </c>
-      <c r="X28">
-        <v>1.18</v>
-      </c>
-      <c r="Y28">
-        <v>1.77</v>
-      </c>
       <c r="Z28">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AA28">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB28">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC28">
         <v>8</v>
       </c>
       <c r="AD28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE28">
         <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AG28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O29">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>3.33</v>
+        <v>2.85</v>
       </c>
       <c r="Q29">
         <v>2.56</v>
@@ -5054,25 +5054,25 @@
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
         <v>2.8</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
         <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z29">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA29">
         <v>2.12</v>
@@ -5081,7 +5081,7 @@
         <v>1.71</v>
       </c>
       <c r="AC29">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD29">
         <v>1.22</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK29">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O30">
         <v>3.64</v>
@@ -5226,16 +5226,16 @@
         <v>1.64</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA30">
         <v>1.49</v>
@@ -5272,7 +5272,7 @@
         <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5368,13 +5368,13 @@
         <v>4.65</v>
       </c>
       <c r="P31">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q31">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R31">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5383,10 +5383,10 @@
         <v>4</v>
       </c>
       <c r="U31">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="V31">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="W31">
         <v>1.18</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK31">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,16 +5528,16 @@
         <v>1.33</v>
       </c>
       <c r="O32">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>1.78</v>
       </c>
       <c r="R32">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S32">
         <v>1.25</v>
@@ -5546,7 +5546,7 @@
         <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V32">
         <v>1.6</v>
@@ -5576,7 +5576,7 @@
         <v>1.53</v>
       </c>
       <c r="AE32">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF32">
         <v>1.85</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>4.41</v>
+        <v>4.7</v>
       </c>
       <c r="Q33">
         <v>2.32</v>
@@ -5706,7 +5706,7 @@
         <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
         <v>2.45</v>
@@ -5724,7 +5724,7 @@
         <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="AA33">
         <v>1.73</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>2.11</v>
@@ -6506,77 +6506,77 @@
         <v>1.65</v>
       </c>
       <c r="O38">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA38">
+        <v>1.95</v>
+      </c>
+      <c r="AB38">
+        <v>1.73</v>
+      </c>
+      <c r="AC38">
+        <v>3.34</v>
+      </c>
+      <c r="AD38">
+        <v>1.24</v>
+      </c>
+      <c r="AE38">
+        <v>1.05</v>
+      </c>
+      <c r="AF38">
+        <v>1.92</v>
+      </c>
+      <c r="AG38">
+        <v>1.77</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.2</v>
+      </c>
+      <c r="AK38">
         <v>2.05</v>
-      </c>
-      <c r="AB38">
-        <v>1.75</v>
-      </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38">
-        <v>0</v>
-      </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
-      <c r="AF38">
-        <v>0</v>
-      </c>
-      <c r="AG38">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
-      <c r="AK38">
-        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6681,7 +6681,7 @@
         <v>2.01</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
         <v>2.88</v>
@@ -6705,7 +6705,7 @@
         <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB39">
         <v>1.73</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -6992,37 +6992,37 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="U41">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
         <v>1.21</v>
@@ -7034,22 +7034,22 @@
         <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC41">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
         <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7176,10 +7176,10 @@
         <v>2.7</v>
       </c>
       <c r="U42">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
         <v>1.05</v>
@@ -7191,16 +7191,16 @@
         <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="AA42">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB42">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC42">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD42">
         <v>1.22</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="Q43">
         <v>2.36</v>
@@ -7339,7 +7339,7 @@
         <v>4</v>
       </c>
       <c r="U43">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V43">
         <v>1.73</v>
@@ -7351,16 +7351,16 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB43">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC43">
         <v>2.1</v>
@@ -7372,10 +7372,10 @@
         <v>1.29</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG43">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P44">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q44">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S44">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T44">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="U44">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="V44">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="W44">
+        <v>1.05</v>
+      </c>
+      <c r="X44">
         <v>1.06</v>
       </c>
-      <c r="X44">
-        <v>1.03</v>
-      </c>
       <c r="Y44">
+        <v>1.44</v>
+      </c>
+      <c r="Z44">
+        <v>2.7</v>
+      </c>
+      <c r="AA44">
+        <v>2.33</v>
+      </c>
+      <c r="AB44">
+        <v>1.51</v>
+      </c>
+      <c r="AC44">
+        <v>5</v>
+      </c>
+      <c r="AD44">
+        <v>1.14</v>
+      </c>
+      <c r="AE44">
+        <v>1.02</v>
+      </c>
+      <c r="AF44">
+        <v>2</v>
+      </c>
+      <c r="AG44">
+        <v>1.7</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.28</v>
       </c>
-      <c r="Z44">
-        <v>3.25</v>
-      </c>
-      <c r="AA44">
-        <v>1.93</v>
-      </c>
-      <c r="AB44">
-        <v>1.75</v>
-      </c>
-      <c r="AC44">
-        <v>3.28</v>
-      </c>
-      <c r="AD44">
-        <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.05</v>
-      </c>
-      <c r="AF44">
-        <v>1.8</v>
-      </c>
-      <c r="AG44">
-        <v>1.9</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.3</v>
-      </c>
       <c r="AK44">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="O45">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="Q45">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V45">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB45">
         <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD45">
         <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7813,7 +7813,7 @@
         <v>3.45</v>
       </c>
       <c r="P46">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q46">
         <v>2.97</v>
@@ -7825,37 +7825,37 @@
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V46">
         <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.4</v>
+        <v>4.52</v>
       </c>
       <c r="AA46">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC46">
         <v>2.88</v>
       </c>
       <c r="AD46">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
         <v>1.14</v>
@@ -7864,7 +7864,7 @@
         <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8145,16 +8145,16 @@
         <v>3.6</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
         <v>1.51</v>
@@ -8172,19 +8172,19 @@
         <v>4.25</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB48">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
         <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
         <v>1.55</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O49">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q49">
         <v>2.84</v>
@@ -8317,13 +8317,13 @@
         <v>3.25</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V49">
         <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8347,13 +8347,13 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
         <v>2.4</v>
@@ -8492,19 +8492,19 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB50">
         <v>2.6</v>
       </c>
       <c r="AC50">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AD50">
         <v>1.62</v>
@@ -8513,10 +8513,10 @@
         <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>2.69</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
         <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="R52">
         <v>2</v>
@@ -8803,7 +8803,7 @@
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U52">
         <v>3.26</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="P53">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q53">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="R53">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U53">
-        <v>2.88</v>
+        <v>3.27</v>
       </c>
       <c r="V53">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z53">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="AA53">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB53">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AC53">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF53">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="O54">
         <v>3.55</v>
       </c>
       <c r="P54">
-        <v>3.31</v>
+        <v>3.95</v>
       </c>
       <c r="Q54">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R54">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="S54">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T54">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U54">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.05</v>
@@ -9150,19 +9150,19 @@
         <v>3.4</v>
       </c>
       <c r="AA54">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB54">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC54">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AD54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF54">
         <v>1.83</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9443,7 +9443,7 @@
         <v>4.1</v>
       </c>
       <c r="P56">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -9458,7 +9458,7 @@
         <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="V56">
         <v>1.5</v>
@@ -9467,7 +9467,7 @@
         <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.23</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O57">
         <v>2.79</v>
@@ -9630,7 +9630,7 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y57">
         <v>1.63</v>
@@ -9642,10 +9642,10 @@
         <v>3.1</v>
       </c>
       <c r="AB57">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC57">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD57">
         <v>1.1</v>
@@ -9654,10 +9654,10 @@
         <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG57">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.24</v>
       </c>
       <c r="AK57">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="O58">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q58">
-        <v>4.32</v>
+        <v>3.53</v>
       </c>
       <c r="R58">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="S58">
         <v>1.25</v>
@@ -9796,19 +9796,19 @@
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z58">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA58">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC58">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AD58">
         <v>1.55</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK58">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9938,43 +9938,43 @@
         <v>4.75</v>
       </c>
       <c r="R59">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S59">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T59">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="U59">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V59">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z59">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA59">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AB59">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC59">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE59">
         <v>1.04</v>
@@ -9983,7 +9983,7 @@
         <v>1.83</v>
       </c>
       <c r="AG59">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>9</v>
       </c>
       <c r="P61">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q61">
         <v>1.4</v>
@@ -10267,22 +10267,22 @@
         <v>3.6</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T61">
         <v>5</v>
       </c>
       <c r="U61">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V61">
         <v>2.05</v>
       </c>
       <c r="W61">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y61">
         <v>1.02</v>
@@ -10297,13 +10297,13 @@
         <v>4.1</v>
       </c>
       <c r="AC61">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD61">
         <v>2.21</v>
       </c>
       <c r="AE61">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AF61">
         <v>1.75</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O62">
         <v>2.65</v>
@@ -10451,16 +10451,16 @@
         <v>1.65</v>
       </c>
       <c r="Z62">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AA62">
         <v>3</v>
       </c>
       <c r="AB62">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC62">
-        <v>6.15</v>
+        <v>6.87</v>
       </c>
       <c r="AD62">
         <v>1.06</v>
@@ -10581,25 +10581,25 @@
         <v>1.06</v>
       </c>
       <c r="O63">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="P63">
-        <v>23</v>
+        <v>21.46</v>
       </c>
       <c r="Q63">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R63">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="S63">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T63">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="U63">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V63">
         <v>1.88</v>
@@ -10620,13 +10620,13 @@
         <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AC63">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD63">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AE63">
         <v>1.39</v>
@@ -10635,7 +10635,7 @@
         <v>2.45</v>
       </c>
       <c r="AG63">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK63">
         <v>9</v>
@@ -10910,58 +10910,58 @@
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q65">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R65">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U65">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V65">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W65">
         <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
         <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA65">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC65">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AD65">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF65">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
+        <v>1.3</v>
+      </c>
+      <c r="AK65">
         <v>1.23</v>
-      </c>
-      <c r="AK65">
-        <v>1.19</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P66">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q66">
         <v>1.79</v>
@@ -11085,16 +11085,16 @@
         <v>1.34</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U66">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11103,7 +11103,7 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="AA66">
         <v>1.83</v>
@@ -11112,19 +11112,19 @@
         <v>1.9</v>
       </c>
       <c r="AC66">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="AD66">
         <v>1.35</v>
       </c>
       <c r="AE66">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF66">
         <v>2.26</v>
       </c>
       <c r="AG66">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O67">
         <v>3.6</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
         <v>2.25</v>
@@ -11248,10 +11248,10 @@
         <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="U67">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V67">
         <v>1.44</v>
@@ -11260,13 +11260,13 @@
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z67">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA67">
         <v>1.67</v>
@@ -11275,16 +11275,16 @@
         <v>2.15</v>
       </c>
       <c r="AC67">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AD67">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG67">
         <v>2.3</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O68">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P68">
         <v>3.3</v>
       </c>
       <c r="Q68">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="R68">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S68">
         <v>1.44</v>
@@ -11414,22 +11414,22 @@
         <v>2.39</v>
       </c>
       <c r="U68">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V68">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y68">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z68">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA68">
         <v>2.38</v>
@@ -11441,16 +11441,16 @@
         <v>4.5</v>
       </c>
       <c r="AD68">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
         <v>2</v>
       </c>
       <c r="AG68">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "45+5", "53", "90+5"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "57"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "57"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "37", "69"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "22", "42"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "36"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1765,14 +1765,14 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2082,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "56", "66"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "77"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "80", "90+2"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2583,11 +2583,11 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "55", "90"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88", "90+2"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "40"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "76"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "55", "83"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "87"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "20", "62", "69"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "80"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "70", "90+2"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4047,14 +4047,14 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,39 +4198,39 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P24">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q24">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="R24">
         <v>1.93</v>
@@ -4242,86 +4242,86 @@
         <v>2.7</v>
       </c>
       <c r="U24">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
         <v>1.34</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="AA24">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB24">
         <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="AD24">
         <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG24">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "45", "85"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK24">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,16 +4361,16 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4380,20 +4380,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
         <v>4.55</v>
       </c>
       <c r="P25">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q25">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R25">
         <v>2.5</v>
@@ -4402,37 +4402,37 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="U25">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
         <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA25">
         <v>1.47</v>
       </c>
       <c r="AB25">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AC25">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AD25">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE25">
         <v>1.22</v>
@@ -4441,50 +4441,50 @@
         <v>1.61</v>
       </c>
       <c r="AG25">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "6", "30"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AJ25">
         <v>1.15</v>
       </c>
       <c r="AK25">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4527,23 +4527,23 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4556,7 +4556,7 @@
         <v>1.85</v>
       </c>
       <c r="Q26">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="R26">
         <v>2.3</v>
@@ -4568,37 +4568,37 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
         <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB26">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
         <v>1.67</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "54", "59", "75"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,36 +4687,36 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O27">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="P27">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>1.97</v>
@@ -4728,28 +4728,28 @@
         <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U27">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
         <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
         <v>3.3</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
         <v>1.83</v>
@@ -4758,7 +4758,7 @@
         <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
@@ -4767,50 +4767,50 @@
         <v>2</v>
       </c>
       <c r="AG27">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "20", "37", "77"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AJ27">
         <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P28">
         <v>3.75</v>
@@ -4897,13 +4897,13 @@
         <v>4.6</v>
       </c>
       <c r="V28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W28">
         <v>1.02</v>
       </c>
       <c r="X28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Y28">
         <v>1.73</v>
@@ -4912,29 +4912,29 @@
         <v>2.03</v>
       </c>
       <c r="AA28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB28">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD28">
         <v>1.04</v>
       </c>
       <c r="AE28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AG28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,13 +5013,13 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5032,17 +5032,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q29">
         <v>2.56</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,33 +5176,33 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O30">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
         <v>2.28</v>
@@ -5223,31 +5223,31 @@
         <v>2.2</v>
       </c>
       <c r="V30">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA30">
         <v>1.49</v>
       </c>
       <c r="AB30">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC30">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD30">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
         <v>1.17</v>
@@ -5256,16 +5256,16 @@
         <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "55"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O31">
         <v>4.65</v>
@@ -5377,10 +5377,10 @@
         <v>2.57</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U31">
         <v>2.03</v>
@@ -5392,13 +5392,13 @@
         <v>1.18</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
         <v>1.44</v>
@@ -5502,36 +5502,36 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
         <v>1.33</v>
       </c>
       <c r="O32">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P32">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q32">
         <v>1.78</v>
@@ -5543,13 +5543,13 @@
         <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="V32">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W32">
         <v>1.15</v>
@@ -5558,35 +5558,35 @@
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z32">
         <v>4.8</v>
       </c>
       <c r="AA32">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB32">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AC32">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AD32">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE32">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "41", "61", "78"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -5677,79 +5677,79 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="Q33">
         <v>2.32</v>
       </c>
       <c r="R33">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
         <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>4.25</v>
+        <v>4.49</v>
       </c>
       <c r="AA33">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AB33">
         <v>2.08</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5847,23 +5847,23 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O34">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P34">
-        <v>5.16</v>
+        <v>5.62</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="S34">
         <v>1.22</v>
@@ -5872,10 +5872,10 @@
         <v>4</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V34">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W34">
         <v>1.14</v>
@@ -5887,32 +5887,32 @@
         <v>1.09</v>
       </c>
       <c r="Z34">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC34">
+        <v>2.2</v>
+      </c>
+      <c r="AD34">
+        <v>1.6</v>
+      </c>
+      <c r="AE34">
+        <v>1.29</v>
+      </c>
+      <c r="AF34">
+        <v>1.57</v>
+      </c>
+      <c r="AG34">
         <v>2.25</v>
       </c>
-      <c r="AD34">
-        <v>1.65</v>
-      </c>
-      <c r="AE34">
-        <v>1.27</v>
-      </c>
-      <c r="AF34">
-        <v>1.53</v>
-      </c>
-      <c r="AG34">
-        <v>2.38</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "15", "38"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,48 +5991,48 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
         <v>1.43</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q35">
         <v>1.94</v>
       </c>
       <c r="R35">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U35">
         <v>2.7</v>
@@ -6044,38 +6044,38 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA35">
         <v>1.82</v>
       </c>
       <c r="AB35">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC35">
         <v>3.18</v>
       </c>
       <c r="AD35">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG35">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "44", "45+4", "55", "86"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
@@ -6087,34 +6087,34 @@
         <v>1.1</v>
       </c>
       <c r="AK35">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O36">
         <v>3.9</v>
@@ -6186,10 +6186,10 @@
         <v>1.6</v>
       </c>
       <c r="Q36">
-        <v>5.22</v>
+        <v>4.32</v>
       </c>
       <c r="R36">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6198,10 +6198,10 @@
         <v>3.5</v>
       </c>
       <c r="U36">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6213,28 +6213,28 @@
         <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AB36">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
         <v>2.4</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
         <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="AK36">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6317,36 +6317,36 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q37">
         <v>4.34</v>
@@ -6394,19 +6394,19 @@
         <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "52", "62", "80", "89"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "83"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>3.35</v>
       </c>
       <c r="P38">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q38">
         <v>2.22</v>
@@ -6696,19 +6696,19 @@
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
         <v>1.33</v>
       </c>
       <c r="Z39">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="AA39">
         <v>2.15</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC39">
         <v>3.8</v>
@@ -6717,13 +6717,13 @@
         <v>1.24</v>
       </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
         <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O40">
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
         <v>2.88</v>
@@ -6859,10 +6859,10 @@
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
         <v>3.2</v>
@@ -6871,10 +6871,10 @@
         <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC40">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD40">
         <v>1.28</v>
@@ -6995,13 +6995,13 @@
         <v>1.75</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
         <v>3.9</v>
       </c>
       <c r="Q41">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
         <v>2.25</v>
@@ -7197,22 +7197,22 @@
         <v>2.02</v>
       </c>
       <c r="AB42">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC42">
         <v>3.6</v>
       </c>
       <c r="AD42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7342,10 +7342,10 @@
         <v>2.05</v>
       </c>
       <c r="V43">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7360,16 +7360,16 @@
         <v>1.44</v>
       </c>
       <c r="AB43">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD43">
         <v>1.73</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
         <v>1.39</v>
@@ -7822,10 +7822,10 @@
         <v>2.13</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
         <v>2.45</v>
@@ -7834,13 +7834,13 @@
         <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
         <v>4.52</v>
@@ -7849,22 +7849,22 @@
         <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC46">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD46">
         <v>1.45</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7985,10 +7985,10 @@
         <v>2</v>
       </c>
       <c r="S47">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T47">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="U47">
         <v>3</v>
@@ -8000,7 +8000,7 @@
         <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
         <v>1.4</v>
@@ -8015,10 +8015,10 @@
         <v>1.7</v>
       </c>
       <c r="AC47">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AD47">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE47">
         <v>1.04</v>
@@ -8027,7 +8027,7 @@
         <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8142,55 +8142,55 @@
         <v>2.19</v>
       </c>
       <c r="Q48">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S48">
         <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AD48">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG48">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8311,19 +8311,19 @@
         <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
         <v>3.25</v>
       </c>
       <c r="U49">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8335,10 +8335,10 @@
         <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB49">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
         <v>2.88</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
         <v>3.6</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8480,10 +8480,10 @@
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -8492,10 +8492,10 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA50">
         <v>1.49</v>
@@ -8504,19 +8504,19 @@
         <v>2.6</v>
       </c>
       <c r="AC50">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD50">
         <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF50">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>3.06</v>
       </c>
       <c r="Q51">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
         <v>1.3</v>
@@ -8649,37 +8649,37 @@
         <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD51">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8791,58 +8791,58 @@
         <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q52">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="R52">
         <v>2</v>
       </c>
       <c r="S52">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T52">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="V52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
         <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AB52">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC52">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD52">
         <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG52">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK52">
         <v>1.37</v>
@@ -8951,13 +8951,13 @@
         <v>2.62</v>
       </c>
       <c r="O53">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="P53">
         <v>2.7</v>
       </c>
       <c r="Q53">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="R53">
         <v>2</v>
@@ -8969,7 +8969,7 @@
         <v>2.6</v>
       </c>
       <c r="U53">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="V53">
         <v>1.34</v>
@@ -8984,13 +8984,13 @@
         <v>1.35</v>
       </c>
       <c r="Z53">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="AA53">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB53">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC53">
         <v>3.9</v>
@@ -9002,7 +9002,7 @@
         <v>1.03</v>
       </c>
       <c r="AF53">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG53">
         <v>1.87</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK53">
         <v>1.49</v>
@@ -9114,10 +9114,10 @@
         <v>1.82</v>
       </c>
       <c r="O54">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
         <v>2.38</v>
@@ -9126,49 +9126,49 @@
         <v>2.03</v>
       </c>
       <c r="S54">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="U54">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA54">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC54">
-        <v>3.59</v>
+        <v>3.29</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF54">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG54">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>1.85</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q55">
         <v>2.46</v>
@@ -9292,7 +9292,7 @@
         <v>1.36</v>
       </c>
       <c r="T55">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U55">
         <v>2.88</v>
@@ -9307,13 +9307,13 @@
         <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA55">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB55">
         <v>1.8</v>
@@ -9443,13 +9443,13 @@
         <v>4.1</v>
       </c>
       <c r="P56">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="Q56">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.34</v>
@@ -9458,43 +9458,43 @@
         <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA56">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AB56">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AC56">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD56">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE56">
         <v>1.14</v>
       </c>
       <c r="AF56">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>2.79</v>
       </c>
       <c r="P57">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9624,13 +9624,13 @@
         <v>3.9</v>
       </c>
       <c r="V57">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W57">
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y57">
         <v>1.63</v>
@@ -9642,7 +9642,7 @@
         <v>3.1</v>
       </c>
       <c r="AB57">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC57">
         <v>6.05</v>
@@ -9654,10 +9654,10 @@
         <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG57">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
+        <v>4</v>
+      </c>
+      <c r="O58">
         <v>3.65</v>
       </c>
-      <c r="O58">
-        <v>3.6</v>
-      </c>
       <c r="P58">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q58">
         <v>3.53</v>
@@ -9808,10 +9808,10 @@
         <v>2.4</v>
       </c>
       <c r="AC58">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD58">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE58">
         <v>1.17</v>
@@ -9935,19 +9935,19 @@
         <v>1.91</v>
       </c>
       <c r="Q59">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="R59">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S59">
         <v>1.36</v>
       </c>
       <c r="T59">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="U59">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V59">
         <v>1.33</v>
@@ -9956,34 +9956,34 @@
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
         <v>1.28</v>
       </c>
       <c r="Z59">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA59">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB59">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC59">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD59">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
+        <v>1.8</v>
+      </c>
+      <c r="AG59">
         <v>1.83</v>
-      </c>
-      <c r="AG59">
-        <v>1.81</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>3.5</v>
       </c>
       <c r="P60">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q60">
         <v>2.47</v>
@@ -10252,58 +10252,58 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O61">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="P61">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q61">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="R61">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="S61">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U61">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V61">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="W61">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z61">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AA61">
         <v>1.2</v>
       </c>
       <c r="AB61">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AC61">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AD61">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AE61">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AF61">
         <v>1.75</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK61">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>2.04</v>
       </c>
       <c r="U62">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="V62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W62">
         <v>1.03</v>
@@ -10457,10 +10457,10 @@
         <v>3</v>
       </c>
       <c r="AB62">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC62">
-        <v>6.87</v>
+        <v>6.88</v>
       </c>
       <c r="AD62">
         <v>1.06</v>
@@ -10593,28 +10593,28 @@
         <v>3.5</v>
       </c>
       <c r="S63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T63">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="U63">
         <v>1.8</v>
       </c>
       <c r="V63">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="W63">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z63">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="AA63">
         <v>1.3</v>
@@ -10626,16 +10626,16 @@
         <v>1.74</v>
       </c>
       <c r="AD63">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AE63">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AF63">
         <v>2.45</v>
       </c>
       <c r="AG63">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Q65">
         <v>4.4</v>
@@ -10925,25 +10925,25 @@
         <v>2.88</v>
       </c>
       <c r="U65">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V65">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
         <v>3.42</v>
       </c>
       <c r="AA65">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB65">
         <v>1.98</v>
@@ -10952,10 +10952,10 @@
         <v>2.97</v>
       </c>
       <c r="AD65">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
         <v>1.72</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O66">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="P66">
         <v>8.5</v>
@@ -11085,16 +11085,16 @@
         <v>1.34</v>
       </c>
       <c r="T66">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V66">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11103,7 +11103,7 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA66">
         <v>1.83</v>
@@ -11112,7 +11112,7 @@
         <v>1.9</v>
       </c>
       <c r="AC66">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="AD66">
         <v>1.35</v>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O67">
         <v>3.6</v>
       </c>
       <c r="P67">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="Q67">
         <v>2.64</v>
       </c>
       <c r="R67">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
         <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="U67">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
         <v>1.08</v>
@@ -11275,13 +11275,13 @@
         <v>2.15</v>
       </c>
       <c r="AC67">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AD67">
         <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
         <v>1.6</v>
@@ -11396,7 +11396,7 @@
         <v>1.98</v>
       </c>
       <c r="O68">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
         <v>3.3</v>
@@ -11411,7 +11411,7 @@
         <v>1.44</v>
       </c>
       <c r="T68">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U68">
         <v>3.4</v>
@@ -11438,7 +11438,7 @@
         <v>1.57</v>
       </c>
       <c r="AC68">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD68">
         <v>1.2</v>

--- a/jogos_2026-10-12.xlsx
+++ b/jogos_2026-10-12.xlsx
@@ -5339,26 +5339,26 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "9", "28", "46", "89"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -6154,26 +6154,26 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "44", "67", "77"]</t>
         </is>
       </c>
       <c r="AJ36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "36", "39", "41"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,26 +6806,26 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "54", "81"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "24", "50", "88"]</t>
         </is>
       </c>
       <c r="AJ40">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -6981,14 +6981,14 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7132,26 +7132,26 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "39", "69"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,26 +7295,26 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "74"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ43">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,16 +7458,16 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -7477,35 +7477,35 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
         <v>2.3</v>
       </c>
       <c r="O44">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
       </c>
       <c r="R44">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S44">
         <v>1.44</v>
       </c>
       <c r="T44">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U44">
         <v>3.25</v>
       </c>
       <c r="V44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W44">
         <v>1.05</v>
@@ -7520,68 +7520,68 @@
         <v>2.7</v>
       </c>
       <c r="AA44">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB44">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC44">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD44">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
+        <v>1.96</v>
+      </c>
+      <c r="AG44">
+        <v>1.73</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>["33"]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>["28"]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.27</v>
+      </c>
+      <c r="AK44">
+        <v>1.55</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>4</v>
+      </c>
+      <c r="AN44">
         <v>2</v>
       </c>
-      <c r="AG44">
-        <v>1.7</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.28</v>
-      </c>
-      <c r="AK44">
-        <v>1.48</v>
-      </c>
-      <c r="AL44">
-        <v>0</v>
-      </c>
-      <c r="AM44">
-        <v>-1</v>
-      </c>
-      <c r="AN44">
-        <v>-1</v>
-      </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,30 +7621,30 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O45">
         <v>3.2</v>
@@ -7665,7 +7665,7 @@
         <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
         <v>1.36</v>
@@ -7689,10 +7689,10 @@
         <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE45">
         <v>1.08</v>
@@ -7701,50 +7701,50 @@
         <v>1.83</v>
       </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+4", "55"]</t>
         </is>
       </c>
       <c r="AJ45">
         <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,26 +7784,26 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "24", "32", "69"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "88"]</t>
         </is>
       </c>
       <c r="AJ46">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,26 +7947,26 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "67"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ47">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,26 +8110,26 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "48", "81", "86"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AJ48">
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8273,16 +8273,16 @@
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ49">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8436,26 +8436,26 @@
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "42", "45+3", "53"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AJ50">
@@ -8538,28 +8538,28 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8599,26 +8599,26 @@
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "76"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AJ51">
@@ -8701,28 +8701,28 @@
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8762,16 +8762,16 @@
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AJ52">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8925,26 +8925,26 @@
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "90+2", "90+10"]</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "54", "90+5"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9088,26 +9088,26 @@
         </is>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "45"]</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "54"]</t>
         </is>
       </c>
       <c r="AJ54">
@@ -9190,25 +9190,25 @@
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT54">
         <v>0</v>
@@ -9251,26 +9251,26 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "56", "77", "85"]</t>
         </is>
       </c>
       <c r="AJ55">
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9903,26 +9903,26 @@
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "72"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "90"]</t>
         </is>
       </c>
       <c r="AJ59">
@@ -10005,28 +10005,28 @@
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O60">
+        <v>3.45</v>
+      </c>
+      <c r="P60">
         <v>3.5</v>
-      </c>
-      <c r="P60">
-        <v>3.15</v>
       </c>
       <c r="Q60">
         <v>2.47</v>
@@ -10119,31 +10119,31 @@
         <v>1.13</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA60">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB60">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC60">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD60">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
         <v>2.17</v>
@@ -10162,7 +10162,7 @@
         <v>1.3</v>
       </c>
       <c r="AK60">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>1.13</v>
       </c>
       <c r="O61">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P61">
         <v>12</v>
@@ -10276,7 +10276,7 @@
         <v>1.72</v>
       </c>
       <c r="V61">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W61">
         <v>1.29</v>
@@ -10297,7 +10297,7 @@
         <v>3.6</v>
       </c>
       <c r="AC61">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD61">
         <v>1.99</v>
@@ -10421,19 +10421,19 @@
         <v>2.65</v>
       </c>
       <c r="P62">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q62">
-        <v>3.32</v>
+        <v>4.28</v>
       </c>
       <c r="R62">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S62">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="T62">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U62">
         <v>4</v>
@@ -10445,25 +10445,25 @@
         <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y62">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z62">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AA62">
         <v>3</v>
       </c>
       <c r="AB62">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC62">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="AD62">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE62">
         <v>1.02</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="O63">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="P63">
-        <v>21.46</v>
+        <v>21</v>
       </c>
       <c r="Q63">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R63">
         <v>3.5</v>
@@ -10617,10 +10617,10 @@
         <v>7.4</v>
       </c>
       <c r="AA63">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB63">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="AC63">
         <v>1.74</v>
@@ -10635,7 +10635,7 @@
         <v>2.45</v>
       </c>
       <c r="AG63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10744,10 +10744,10 @@
         <v>2.88</v>
       </c>
       <c r="O64">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q64">
         <v>3.6</v>
@@ -10759,7 +10759,7 @@
         <v>1.41</v>
       </c>
       <c r="T64">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="U64">
         <v>2.84</v>
@@ -10771,13 +10771,13 @@
         <v>1.05</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
         <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA64">
         <v>2.1</v>
@@ -10792,13 +10792,13 @@
         <v>1.21</v>
       </c>
       <c r="AE64">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
         <v>1.8</v>
       </c>
       <c r="AG64">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q65">
         <v>4.4</v>
@@ -11070,7 +11070,7 @@
         <v>1.33</v>
       </c>
       <c r="O66">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P66">
         <v>8.5</v>
@@ -11079,10 +11079,10 @@
         <v>1.79</v>
       </c>
       <c r="R66">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="S66">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
         <v>3</v>
@@ -11103,7 +11103,7 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="AA66">
         <v>1.83</v>
@@ -11112,19 +11112,19 @@
         <v>1.9</v>
       </c>
       <c r="AC66">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="AD66">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE66">
         <v>1.07</v>
       </c>
       <c r="AF66">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AG66">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="Q67">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
         <v>3.34</v>
       </c>
       <c r="U67">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="V67">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA67">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC67">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AD67">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE67">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG67">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O68">
         <v>3.2</v>
@@ -11402,10 +11402,10 @@
         <v>3.3</v>
       </c>
       <c r="Q68">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S68">
         <v>1.44</v>
@@ -11429,28 +11429,28 @@
         <v>1.4</v>
       </c>
       <c r="Z68">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AA68">
         <v>2.38</v>
       </c>
       <c r="AB68">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC68">
         <v>4.6</v>
       </c>
       <c r="AD68">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE68">
         <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG68">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
-        <v>4.5</v>
+        <v>5.59</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC69">
         <v>0</v>
